--- a/타임테이블.xlsx
+++ b/타임테이블.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.286.56066"/>
+  <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.292.56109"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="590" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
   <si>
     <t>ㅡ</t>
   </si>
@@ -150,6 +150,282 @@
   </si>
   <si>
     <t>2026.01.23</t>
+  </si>
+  <si>
+    <t>기획</t>
+  </si>
+  <si>
+    <t>프론트엔드</t>
+  </si>
+  <si>
+    <t>메인페이지 작업</t>
+  </si>
+  <si>
+    <t>5D</t>
+  </si>
+  <si>
+    <t>6D</t>
+  </si>
+  <si>
+    <t>7D</t>
+  </si>
+  <si>
+    <t>8D</t>
+  </si>
+  <si>
+    <t>9D</t>
+  </si>
+  <si>
+    <t>12D</t>
+  </si>
+  <si>
+    <t>13D</t>
+  </si>
+  <si>
+    <t>14D</t>
+  </si>
+  <si>
+    <t>15D</t>
+  </si>
+  <si>
+    <t>16D</t>
+  </si>
+  <si>
+    <t>19D</t>
+  </si>
+  <si>
+    <t>20D</t>
+  </si>
+  <si>
+    <t>21D</t>
+  </si>
+  <si>
+    <t>22D</t>
+  </si>
+  <si>
+    <t>23D</t>
+  </si>
+  <si>
+    <t>2W</t>
+  </si>
+  <si>
+    <t>3W</t>
+  </si>
+  <si>
+    <t>공동</t>
+  </si>
+  <si>
+    <t>프로젝트 구상</t>
+  </si>
+  <si>
+    <t>23일</t>
+  </si>
+  <si>
+    <t>24일</t>
+  </si>
+  <si>
+    <t>25일</t>
+  </si>
+  <si>
+    <t>26일</t>
+  </si>
+  <si>
+    <t>27일</t>
+  </si>
+  <si>
+    <t>28일</t>
+  </si>
+  <si>
+    <t>29일</t>
+  </si>
+  <si>
+    <t>30일</t>
+  </si>
+  <si>
+    <t>31일</t>
+  </si>
+  <si>
+    <t>32일</t>
+  </si>
+  <si>
+    <t>33일</t>
+  </si>
+  <si>
+    <t>34일</t>
+  </si>
+  <si>
+    <t>35일</t>
+  </si>
+  <si>
+    <t>36일</t>
+  </si>
+  <si>
+    <t>37일</t>
+  </si>
+  <si>
+    <t>38일</t>
+  </si>
+  <si>
+    <t>39일</t>
+  </si>
+  <si>
+    <t>40일</t>
+  </si>
+  <si>
+    <t>41일</t>
+  </si>
+  <si>
+    <t>42일</t>
+  </si>
+  <si>
+    <t>43일</t>
+  </si>
+  <si>
+    <t>44일</t>
+  </si>
+  <si>
+    <t>45일</t>
+  </si>
+  <si>
+    <t>46일</t>
+  </si>
+  <si>
+    <t>47일</t>
+  </si>
+  <si>
+    <t>48일</t>
+  </si>
+  <si>
+    <t>프로젝트 기획 및 구상</t>
+  </si>
+  <si>
+    <t>4일</t>
+  </si>
+  <si>
+    <t>완료</t>
+  </si>
+  <si>
+    <t>메인페이지 기본 틀  작업</t>
+  </si>
+  <si>
+    <t>1일</t>
+  </si>
+  <si>
+    <t>김태완</t>
+  </si>
+  <si>
+    <t>김민준</t>
+  </si>
+  <si>
+    <t>김성연</t>
+  </si>
+  <si>
+    <t>메인페이지</t>
+  </si>
+  <si>
+    <t>미세먼지 페이지</t>
+  </si>
+  <si>
+    <t>옷차림 추천 페이지</t>
+  </si>
+  <si>
+    <t>옷차림 추천 상세 페이지</t>
+  </si>
+  <si>
+    <t>백엔드</t>
+  </si>
+  <si>
+    <t>로그인 페이지</t>
+  </si>
+  <si>
+    <t>로그인 / 회원가입 페이지</t>
+  </si>
+  <si>
+    <t>커뮤니티 페이지</t>
+  </si>
+  <si>
+    <t>로그인 / 회원가입 로직</t>
+  </si>
+  <si>
+    <t>로그인 회원가입</t>
+  </si>
+  <si>
+    <t>로그인 / 회원가입</t>
+  </si>
+  <si>
+    <t>소셜로그인</t>
+  </si>
+  <si>
+    <t>일반 로컬 로그인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">실시간 </t>
+  </si>
+  <si>
+    <t>실시간 날씨 정보</t>
+  </si>
+  <si>
+    <t>실시간 대기질 정보</t>
+  </si>
+  <si>
+    <t>예보 카드</t>
+  </si>
+  <si>
+    <t>기상 특보</t>
+  </si>
+  <si>
+    <t>실시간 날씨 지도</t>
+  </si>
+  <si>
+    <t>옷차림 추천 상세 페이지 구현</t>
+  </si>
+  <si>
+    <t>옷차림 추천 페이지 구현</t>
+  </si>
+  <si>
+    <t>통계 페이지 구현</t>
+  </si>
+  <si>
+    <t>예보요약카드</t>
+  </si>
+  <si>
+    <t>커뮤니티 인기글 목록</t>
+  </si>
+  <si>
+    <t>지역별 날씨 목록</t>
+  </si>
+  <si>
+    <t xml:space="preserve">실시간 날씨 정보 / </t>
+  </si>
+  <si>
+    <t>실시간 날씨 정보 / 실시간 대기질 정보 / 예보 카드</t>
+  </si>
+  <si>
+    <t>실시간 날씨 정보 / 실시간 대기질 정보 / 예보 카드 / 예보 요약카드</t>
+  </si>
+  <si>
+    <t>기상 특보 / 지역별 날씨 목록</t>
+  </si>
+  <si>
+    <t>역할 분배</t>
+  </si>
+  <si>
+    <t>프로젝트 역할 분배</t>
+  </si>
+  <si>
+    <t>주석 정리</t>
+  </si>
+  <si>
+    <t>주석 정리 / 최적화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">실시간 대기질 상세패널 / 측정소 정보 / </t>
+  </si>
+  <si>
+    <t>실시간 대기질 상세패널 / 측정소 정보 / 관련 사이트</t>
+  </si>
+  <si>
+    <t>지역별 대기질</t>
   </si>
 </sst>
 </file>
@@ -157,7 +433,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="34">
+  <fonts count="57">
     <font>
       <sz val="11.0"/>
       <name val="맑은 고딕"/>
@@ -336,17 +612,141 @@
     <font>
       <b/>
       <sz val="11.0"/>
+      <name val="Pretendard Light"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24.0"/>
+      <name val="Pretendard Light"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="24.0"/>
+      <name val="Pretendard Light"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24.0"/>
       <name val="맑은 고딕"/>
       <color theme="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="15.0"/>
       <name val="Pretendard Light"/>
       <color theme="1"/>
     </font>
+    <font>
+      <sz val="15.0"/>
+      <name val="Pretendard Light"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15.0"/>
+      <name val="맑은 고딕"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="15.0"/>
+      <name val="맑은 고딕"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="13.0"/>
+      <name val="맑은 고딕"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="13.0"/>
+      <name val="Pretendard Light"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15.0"/>
+      <name val="돋움"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="15.0"/>
+      <name val="돋움"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="13.0"/>
+      <name val="돋움"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="돋움"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15.0"/>
+      <name val="배달의민족 도현"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="15.0"/>
+      <name val="배달의민족 도현"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="13.0"/>
+      <name val="배달의민족 도현"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="배달의민족 도현"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <name val="배달의민족 도현"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="배달의민족 도현"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14.0"/>
+      <name val="배달의민족 도현"/>
+      <color rgb="FF626262"/>
+    </font>
+    <font>
+      <sz val="14.0"/>
+      <name val="배달의민족 도현"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.0"/>
+      <name val="배달의민족 도현"/>
+      <color rgb="FF626262"/>
+    </font>
+    <font>
+      <sz val="13.0"/>
+      <name val="배달의민족 도현"/>
+      <color rgb="FFFF0000"/>
+    </font>
+    <font>
+      <sz val="13.0"/>
+      <name val="배달의민족 도현"/>
+      <color rgb="FFFFFF00"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -542,14 +942,61 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9933"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC099"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFC0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0ECFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC0FF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFC6600"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="42">
+  <borders count="61">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -564,7 +1011,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -573,7 +1019,6 @@
       <bottom style="thick">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -582,7 +1027,6 @@
       <bottom style="thick">
         <color rgb="FFACCCEA"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -591,7 +1035,6 @@
       <bottom style="medium">
         <color theme="4" tint="0.399980"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -606,7 +1049,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -621,7 +1063,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -636,7 +1077,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -645,7 +1085,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -656,7 +1095,6 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -667,7 +1105,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -676,7 +1113,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -687,7 +1123,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -696,7 +1131,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -705,7 +1139,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -716,7 +1149,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -725,7 +1157,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -736,7 +1167,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -747,7 +1177,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -756,7 +1185,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -767,7 +1195,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -776,7 +1203,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -785,7 +1211,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thick">
@@ -796,7 +1221,6 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -805,7 +1229,6 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -816,7 +1239,6 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -829,7 +1251,6 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -840,7 +1261,6 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -853,7 +1273,6 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -864,7 +1283,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -873,7 +1291,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -884,7 +1301,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -895,7 +1311,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -910,7 +1325,6 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -923,7 +1337,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -936,7 +1349,6 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -947,7 +1359,6 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -956,7 +1367,6 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -967,7 +1377,6 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -976,7 +1385,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -985,7 +1393,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -996,7 +1403,246 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="49">
@@ -1148,7 +1794,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="216">
+  <cellXfs count="559">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1770,32 +2416,1061 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="39" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="40" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="36" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="38" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="39" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="40" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="36" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="38" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="39" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="40" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="36" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="38" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="39" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="40" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="36" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="38" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="39" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="40" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="36" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="38" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="39" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="40" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="36" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="38" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="33" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="33" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="33" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="33" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="33" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="34" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="34" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="34" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="34" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="34" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="35" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="35" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="36" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="36" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="37" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="37" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="37" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="37" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="37" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="37" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="37" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="37" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="36" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="36" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="35" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="35" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="38" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="39" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="40" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="48" fillId="35" borderId="33" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="40" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="48" fillId="35" borderId="42" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="40" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="40" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="37" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="37" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="37" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="37" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="37" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="37" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="48" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="40" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="40" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="37" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="37" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="37" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="40" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="36" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="40" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2115,55 +3790,72 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:AJ37"/>
+  <dimension ref="B1:AJ40"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
-    <col min="17" max="17" width="7.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="18" max="18" width="7.63000011" customWidth="1" outlineLevel="0"/>
-    <col min="19" max="36" width="3.88000011" customWidth="1" outlineLevel="0"/>
+    <col min="10" max="15" width="12.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="16" max="16" width="8.13000011" customWidth="1" outlineLevel="0"/>
+    <col min="17" max="18" width="9.13000011" customWidth="1" outlineLevel="0"/>
+    <col min="19" max="19" width="4.75500011" customWidth="1" outlineLevel="0"/>
+    <col min="20" max="20" width="4.88000011" customWidth="1" outlineLevel="0"/>
+    <col min="21" max="21" width="5.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="22" max="22" width="4.88000011" customWidth="1" outlineLevel="0"/>
+    <col min="23" max="23" width="5.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="24" max="24" width="4.88000011" customWidth="1" outlineLevel="0"/>
+    <col min="25" max="25" width="5.75500011" customWidth="1" outlineLevel="0"/>
+    <col min="26" max="26" width="5.88000011" customWidth="1" outlineLevel="0"/>
+    <col min="27" max="27" width="6.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="28" max="28" width="5.88000011" customWidth="1" outlineLevel="0"/>
+    <col min="29" max="29" width="6.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="30" max="30" width="5.88000011" customWidth="1" outlineLevel="0"/>
+    <col min="31" max="31" width="6.50500011" customWidth="1" outlineLevel="0"/>
+    <col min="32" max="32" width="5.75500011" customWidth="1" outlineLevel="0"/>
+    <col min="33" max="33" width="6.25500011" customWidth="1" outlineLevel="0"/>
+    <col min="34" max="34" width="6.38000011" customWidth="1" outlineLevel="0"/>
+    <col min="35" max="36" width="3.88000011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:36" ht="17.250000" customHeight="1">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="344" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="62" t="s">
+      <c r="C2" s="346"/>
+      <c r="D2" s="420" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="61"/>
+      <c r="E2" s="421"/>
+      <c r="F2" s="421"/>
+      <c r="G2" s="421"/>
+      <c r="H2" s="421"/>
+      <c r="I2" s="422"/>
     </row>
     <row r="3" spans="2:36">
-      <c r="B3" s="66" t="s">
+      <c r="B3" s="423" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="71"/>
-      <c r="D3" s="66" t="s">
+      <c r="C3" s="424"/>
+      <c r="D3" s="423" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="71"/>
+      <c r="E3" s="425"/>
+      <c r="F3" s="425"/>
+      <c r="G3" s="425"/>
+      <c r="H3" s="425"/>
+      <c r="I3" s="424"/>
     </row>
     <row r="4" spans="2:36" ht="17.250000">
-      <c r="B4" s="64" t="s">
+      <c r="B4" s="426" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="57" t="s">
+      <c r="C4" s="421"/>
+      <c r="D4" s="344" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="63"/>
+      <c r="E4" s="346"/>
+      <c r="F4" s="346"/>
+      <c r="G4" s="346"/>
+      <c r="H4" s="346"/>
+      <c r="I4" s="345"/>
     </row>
     <row r="5" spans="2:36">
       <c r="B5" s="73"/>
@@ -2205,1189 +3897,1428 @@
       <c r="H8" s="48"/>
       <c r="I8" s="48"/>
     </row>
-    <row r="9" spans="2:36" ht="17.250000" customHeight="1">
-      <c r="B9" s="160" t="s">
+    <row r="9" spans="2:36" ht="18.000000">
+      <c r="B9" s="501" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="161"/>
-      <c r="D9" s="160" t="s">
+      <c r="C9" s="502"/>
+      <c r="D9" s="502" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="161"/>
-      <c r="F9" s="160" t="s">
+      <c r="E9" s="502"/>
+      <c r="F9" s="502" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="183"/>
-      <c r="H9" s="183"/>
-      <c r="I9" s="161"/>
-      <c r="J9" s="160" t="s">
+      <c r="G9" s="502"/>
+      <c r="H9" s="502"/>
+      <c r="I9" s="502"/>
+      <c r="J9" s="502" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="183"/>
-      <c r="L9" s="183"/>
-      <c r="M9" s="183"/>
-      <c r="N9" s="183"/>
-      <c r="O9" s="161"/>
-      <c r="P9" s="208" t="s">
+      <c r="K9" s="502"/>
+      <c r="L9" s="502"/>
+      <c r="M9" s="502"/>
+      <c r="N9" s="502"/>
+      <c r="O9" s="502"/>
+      <c r="P9" s="502" t="s">
         <v>10</v>
       </c>
-      <c r="Q9" s="208" t="s">
+      <c r="Q9" s="502" t="s">
         <v>11</v>
       </c>
-      <c r="R9" s="208" t="s">
+      <c r="R9" s="502" t="s">
         <v>13</v>
       </c>
-      <c r="S9" s="209" t="s">
+      <c r="S9" s="503" t="s">
         <v>14</v>
       </c>
-      <c r="T9" s="210" t="s">
+      <c r="T9" s="502" t="s">
         <v>21</v>
       </c>
-      <c r="U9" s="211"/>
-      <c r="V9" s="211"/>
-      <c r="W9" s="211"/>
-      <c r="X9" s="211"/>
-      <c r="Y9" s="211"/>
-      <c r="Z9" s="211"/>
-      <c r="AA9" s="211"/>
-      <c r="AB9" s="211"/>
-      <c r="AC9" s="211"/>
-      <c r="AD9" s="211"/>
-      <c r="AE9" s="211"/>
-      <c r="AF9" s="211"/>
-      <c r="AG9" s="211"/>
-      <c r="AH9" s="212"/>
+      <c r="U9" s="502"/>
+      <c r="V9" s="502"/>
+      <c r="W9" s="502"/>
+      <c r="X9" s="502"/>
+      <c r="Y9" s="502"/>
+      <c r="Z9" s="502"/>
+      <c r="AA9" s="502"/>
+      <c r="AB9" s="502"/>
+      <c r="AC9" s="502"/>
+      <c r="AD9" s="502"/>
+      <c r="AE9" s="502"/>
+      <c r="AF9" s="502"/>
+      <c r="AG9" s="502"/>
+      <c r="AH9" s="504"/>
     </row>
-    <row r="10" spans="2:36" ht="28.500000" customHeight="1">
-      <c r="B10" s="173"/>
-      <c r="C10" s="174"/>
-      <c r="D10" s="173"/>
-      <c r="E10" s="174"/>
-      <c r="F10" s="173"/>
-      <c r="G10" s="184"/>
-      <c r="H10" s="184"/>
-      <c r="I10" s="174"/>
-      <c r="J10" s="173"/>
-      <c r="K10" s="184"/>
-      <c r="L10" s="184"/>
-      <c r="M10" s="184"/>
-      <c r="N10" s="184"/>
-      <c r="O10" s="174"/>
-      <c r="P10" s="213"/>
-      <c r="Q10" s="213"/>
-      <c r="R10" s="213"/>
-      <c r="S10" s="209" t="s">
+    <row r="10" spans="2:36" ht="18.000000">
+      <c r="B10" s="505"/>
+      <c r="C10" s="499"/>
+      <c r="D10" s="499"/>
+      <c r="E10" s="499"/>
+      <c r="F10" s="499"/>
+      <c r="G10" s="499"/>
+      <c r="H10" s="499"/>
+      <c r="I10" s="499"/>
+      <c r="J10" s="499"/>
+      <c r="K10" s="499"/>
+      <c r="L10" s="499"/>
+      <c r="M10" s="499"/>
+      <c r="N10" s="499"/>
+      <c r="O10" s="499"/>
+      <c r="P10" s="499"/>
+      <c r="Q10" s="499"/>
+      <c r="R10" s="499"/>
+      <c r="S10" s="500" t="s">
         <v>15</v>
       </c>
-      <c r="T10" s="210" t="s">
-        <v>19</v>
-      </c>
-      <c r="U10" s="211"/>
-      <c r="V10" s="211"/>
-      <c r="W10" s="211"/>
-      <c r="X10" s="212"/>
-      <c r="Y10" s="210" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z10" s="211"/>
-      <c r="AA10" s="211"/>
-      <c r="AB10" s="211"/>
-      <c r="AC10" s="212"/>
-      <c r="AD10" s="210" t="s">
-        <v>20</v>
-      </c>
-      <c r="AE10" s="211"/>
-      <c r="AF10" s="211"/>
-      <c r="AG10" s="211"/>
-      <c r="AH10" s="212"/>
+      <c r="T10" s="499" t="s">
+        <v>17</v>
+      </c>
+      <c r="U10" s="499"/>
+      <c r="V10" s="499"/>
+      <c r="W10" s="499"/>
+      <c r="X10" s="499"/>
+      <c r="Y10" s="499" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z10" s="499"/>
+      <c r="AA10" s="499"/>
+      <c r="AB10" s="499"/>
+      <c r="AC10" s="499"/>
+      <c r="AD10" s="499" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE10" s="499"/>
+      <c r="AF10" s="499"/>
+      <c r="AG10" s="499"/>
+      <c r="AH10" s="506"/>
       <c r="AI10" s="23"/>
       <c r="AJ10" s="23"/>
     </row>
-    <row r="11" spans="2:36" ht="17.250000" customHeight="1">
-      <c r="B11" s="85"/>
-      <c r="C11" s="89"/>
-      <c r="D11" s="175"/>
-      <c r="E11" s="176"/>
-      <c r="F11" s="175"/>
-      <c r="G11" s="185"/>
-      <c r="H11" s="185"/>
-      <c r="I11" s="176"/>
-      <c r="J11" s="175"/>
-      <c r="K11" s="185"/>
-      <c r="L11" s="185"/>
-      <c r="M11" s="185"/>
-      <c r="N11" s="185"/>
-      <c r="O11" s="176"/>
-      <c r="P11" s="214"/>
-      <c r="Q11" s="214"/>
-      <c r="R11" s="214"/>
-      <c r="S11" s="215" t="s">
+    <row r="11" spans="2:36" ht="18.000000">
+      <c r="B11" s="507"/>
+      <c r="C11" s="500"/>
+      <c r="D11" s="499"/>
+      <c r="E11" s="499"/>
+      <c r="F11" s="499"/>
+      <c r="G11" s="499"/>
+      <c r="H11" s="499"/>
+      <c r="I11" s="499"/>
+      <c r="J11" s="499"/>
+      <c r="K11" s="499"/>
+      <c r="L11" s="499"/>
+      <c r="M11" s="499"/>
+      <c r="N11" s="499"/>
+      <c r="O11" s="499"/>
+      <c r="P11" s="500"/>
+      <c r="Q11" s="500"/>
+      <c r="R11" s="500"/>
+      <c r="S11" s="500" t="s">
         <v>16</v>
       </c>
-      <c r="T11" s="215" t="s">
-        <v>24</v>
-      </c>
-      <c r="U11" s="215" t="s">
-        <v>25</v>
-      </c>
-      <c r="V11" s="215" t="s">
-        <v>26</v>
-      </c>
-      <c r="W11" s="215" t="s">
-        <v>27</v>
-      </c>
-      <c r="X11" s="215" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y11" s="215" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z11" s="215" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA11" s="215" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB11" s="215" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC11" s="215" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD11" s="215" t="s">
-        <v>34</v>
-      </c>
-      <c r="AE11" s="215" t="s">
-        <v>35</v>
-      </c>
-      <c r="AF11" s="215" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG11" s="215" t="s">
-        <v>37</v>
-      </c>
-      <c r="AH11" s="215" t="s">
-        <v>38</v>
+      <c r="T11" s="500" t="s">
+        <v>45</v>
+      </c>
+      <c r="U11" s="500" t="s">
+        <v>46</v>
+      </c>
+      <c r="V11" s="500" t="s">
+        <v>47</v>
+      </c>
+      <c r="W11" s="500" t="s">
+        <v>48</v>
+      </c>
+      <c r="X11" s="500" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y11" s="500" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z11" s="500" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA11" s="500" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB11" s="500" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC11" s="500" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD11" s="500" t="s">
+        <v>55</v>
+      </c>
+      <c r="AE11" s="500" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF11" s="500" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG11" s="500" t="s">
+        <v>58</v>
+      </c>
+      <c r="AH11" s="508" t="s">
+        <v>59</v>
       </c>
       <c r="AI11" s="23"/>
       <c r="AJ11" s="23"/>
     </row>
-    <row r="12" spans="2:36" ht="17.250000">
-      <c r="B12" s="93"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="57"/>
-      <c r="K12" s="58"/>
-      <c r="L12" s="90"/>
-      <c r="M12" s="90"/>
-      <c r="N12" s="90"/>
-      <c r="O12" s="91"/>
-      <c r="P12" s="77" t="s">
+    <row r="12" spans="2:36" ht="17.250000" customHeight="1">
+      <c r="B12" s="476" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="465"/>
+      <c r="D12" s="545" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="546"/>
+      <c r="F12" s="466" t="s">
+        <v>90</v>
+      </c>
+      <c r="G12" s="466"/>
+      <c r="H12" s="466"/>
+      <c r="I12" s="466"/>
+      <c r="J12" s="466"/>
+      <c r="K12" s="466"/>
+      <c r="L12" s="466"/>
+      <c r="M12" s="466"/>
+      <c r="N12" s="466"/>
+      <c r="O12" s="466"/>
+      <c r="P12" s="466" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q12" s="467">
+        <v>1</v>
+      </c>
+      <c r="R12" s="466" t="s">
+        <v>91</v>
+      </c>
+      <c r="S12" s="468"/>
+      <c r="T12" s="468"/>
+      <c r="U12" s="468"/>
+      <c r="V12" s="466"/>
+      <c r="W12" s="466"/>
+      <c r="X12" s="466"/>
+      <c r="Y12" s="466"/>
+      <c r="Z12" s="466"/>
+      <c r="AA12" s="466"/>
+      <c r="AB12" s="466"/>
+      <c r="AC12" s="466"/>
+      <c r="AD12" s="466"/>
+      <c r="AE12" s="466"/>
+      <c r="AF12" s="466"/>
+      <c r="AG12" s="466"/>
+      <c r="AH12" s="477"/>
+    </row>
+    <row r="13" spans="2:36" ht="17.250000" customHeight="1">
+      <c r="B13" s="476"/>
+      <c r="C13" s="465"/>
+      <c r="D13" s="547"/>
+      <c r="E13" s="548"/>
+      <c r="F13" s="466" t="s">
+        <v>128</v>
+      </c>
+      <c r="G13" s="466"/>
+      <c r="H13" s="466"/>
+      <c r="I13" s="466"/>
+      <c r="J13" s="466"/>
+      <c r="K13" s="466"/>
+      <c r="L13" s="466"/>
+      <c r="M13" s="466"/>
+      <c r="N13" s="466"/>
+      <c r="O13" s="466"/>
+      <c r="P13" s="466" t="s">
         <v>22</v>
       </c>
-      <c r="Q12" s="92" t="s">
+      <c r="Q13" s="469" t="s">
         <v>23</v>
       </c>
-      <c r="R12" s="77"/>
-      <c r="S12" s="77"/>
-      <c r="T12" s="77"/>
-      <c r="U12" s="77"/>
-      <c r="V12" s="77"/>
-      <c r="W12" s="77"/>
-      <c r="X12" s="77"/>
-      <c r="Y12" s="77"/>
-      <c r="Z12" s="77"/>
-      <c r="AA12" s="77"/>
-      <c r="AB12" s="77"/>
-      <c r="AC12" s="77"/>
-      <c r="AD12" s="77"/>
-      <c r="AE12" s="77"/>
-      <c r="AF12" s="77"/>
-      <c r="AG12" s="77"/>
-      <c r="AH12" s="77"/>
+      <c r="R13" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S13" s="466"/>
+      <c r="T13" s="466"/>
+      <c r="U13" s="470"/>
+      <c r="V13" s="466"/>
+      <c r="W13" s="466"/>
+      <c r="X13" s="466"/>
+      <c r="Y13" s="466"/>
+      <c r="Z13" s="466"/>
+      <c r="AA13" s="466"/>
+      <c r="AB13" s="466"/>
+      <c r="AC13" s="466"/>
+      <c r="AD13" s="466"/>
+      <c r="AE13" s="466"/>
+      <c r="AF13" s="466"/>
+      <c r="AG13" s="466"/>
+      <c r="AH13" s="477"/>
     </row>
-    <row r="13" spans="2:36" ht="17.250000">
-      <c r="B13" s="93"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="57"/>
-      <c r="K13" s="58"/>
-      <c r="L13" s="90"/>
-      <c r="M13" s="90"/>
-      <c r="N13" s="90"/>
-      <c r="O13" s="91"/>
-      <c r="P13" s="77" t="s">
+    <row r="14" spans="2:36" ht="17.250000" customHeight="1">
+      <c r="B14" s="476"/>
+      <c r="C14" s="465"/>
+      <c r="D14" s="460" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14" s="460"/>
+      <c r="F14" s="460" t="s">
+        <v>130</v>
+      </c>
+      <c r="G14" s="460"/>
+      <c r="H14" s="460"/>
+      <c r="I14" s="460"/>
+      <c r="J14" s="460"/>
+      <c r="K14" s="460"/>
+      <c r="L14" s="460"/>
+      <c r="M14" s="460"/>
+      <c r="N14" s="460"/>
+      <c r="O14" s="460"/>
+      <c r="P14" s="460" t="s">
         <v>22</v>
       </c>
-      <c r="Q13" s="92" t="s">
+      <c r="Q14" s="471" t="s">
         <v>23</v>
       </c>
-      <c r="R13" s="77"/>
-      <c r="S13" s="77"/>
-      <c r="T13" s="77"/>
-      <c r="U13" s="77"/>
-      <c r="V13" s="77"/>
-      <c r="W13" s="77"/>
-      <c r="X13" s="77"/>
-      <c r="Y13" s="77"/>
-      <c r="Z13" s="77"/>
-      <c r="AA13" s="77"/>
-      <c r="AB13" s="77"/>
-      <c r="AC13" s="77"/>
-      <c r="AD13" s="77"/>
-      <c r="AE13" s="77"/>
-      <c r="AF13" s="77"/>
-      <c r="AG13" s="77"/>
-      <c r="AH13" s="77"/>
+      <c r="R14" s="466" t="s">
+        <v>94</v>
+      </c>
+      <c r="S14" s="460"/>
+      <c r="T14" s="460"/>
+      <c r="U14" s="470"/>
+      <c r="V14" s="460"/>
+      <c r="W14" s="460"/>
+      <c r="X14" s="460"/>
+      <c r="Y14" s="460"/>
+      <c r="Z14" s="460"/>
+      <c r="AA14" s="460"/>
+      <c r="AB14" s="460"/>
+      <c r="AC14" s="460"/>
+      <c r="AD14" s="460"/>
+      <c r="AE14" s="460"/>
+      <c r="AF14" s="460"/>
+      <c r="AG14" s="460"/>
+      <c r="AH14" s="478"/>
     </row>
-    <row r="14" spans="2:36" ht="17.250000">
-      <c r="B14" s="93"/>
-      <c r="C14" s="94"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="58"/>
-      <c r="L14" s="90"/>
-      <c r="M14" s="90"/>
-      <c r="N14" s="90"/>
-      <c r="O14" s="91"/>
-      <c r="P14" s="77" t="s">
+    <row r="15" spans="2:36" ht="17.250000" customHeight="1">
+      <c r="B15" s="476" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="465"/>
+      <c r="D15" s="530" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="531"/>
+      <c r="F15" s="530" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="540"/>
+      <c r="H15" s="540"/>
+      <c r="I15" s="531"/>
+      <c r="J15" s="460" t="s">
+        <v>125</v>
+      </c>
+      <c r="K15" s="460"/>
+      <c r="L15" s="460"/>
+      <c r="M15" s="460"/>
+      <c r="N15" s="460"/>
+      <c r="O15" s="460"/>
+      <c r="P15" s="460" t="s">
         <v>22</v>
       </c>
-      <c r="Q14" s="92" t="s">
+      <c r="Q15" s="471" t="s">
         <v>23</v>
       </c>
-      <c r="R14" s="77"/>
-      <c r="S14" s="77"/>
-      <c r="T14" s="77"/>
-      <c r="U14" s="77"/>
-      <c r="V14" s="77"/>
-      <c r="W14" s="77"/>
-      <c r="X14" s="77"/>
-      <c r="Y14" s="77"/>
-      <c r="Z14" s="77"/>
-      <c r="AA14" s="77"/>
-      <c r="AB14" s="77"/>
-      <c r="AC14" s="77"/>
-      <c r="AD14" s="77"/>
-      <c r="AE14" s="77"/>
-      <c r="AF14" s="77"/>
-      <c r="AG14" s="77"/>
-      <c r="AH14" s="77"/>
+      <c r="R15" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S15" s="460"/>
+      <c r="T15" s="460"/>
+      <c r="U15" s="460"/>
+      <c r="V15" s="460"/>
+      <c r="W15" s="460"/>
+      <c r="X15" s="460"/>
+      <c r="Y15" s="460"/>
+      <c r="Z15" s="460"/>
+      <c r="AA15" s="460"/>
+      <c r="AB15" s="460"/>
+      <c r="AC15" s="460"/>
+      <c r="AD15" s="460"/>
+      <c r="AE15" s="460"/>
+      <c r="AF15" s="460"/>
+      <c r="AG15" s="460"/>
+      <c r="AH15" s="478"/>
     </row>
-    <row r="15" spans="2:36" ht="17.250000">
-      <c r="B15" s="93"/>
-      <c r="C15" s="94"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="63"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="58"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="58"/>
-      <c r="L15" s="90"/>
-      <c r="M15" s="90"/>
-      <c r="N15" s="90"/>
-      <c r="O15" s="91"/>
-      <c r="P15" s="77" t="s">
+    <row r="16" spans="2:36" ht="17.250000" customHeight="1">
+      <c r="B16" s="476"/>
+      <c r="C16" s="465"/>
+      <c r="D16" s="542"/>
+      <c r="E16" s="543"/>
+      <c r="F16" s="542"/>
+      <c r="G16" s="494"/>
+      <c r="H16" s="494"/>
+      <c r="I16" s="543"/>
+      <c r="J16" s="460" t="s">
+        <v>126</v>
+      </c>
+      <c r="K16" s="460"/>
+      <c r="L16" s="460"/>
+      <c r="M16" s="460"/>
+      <c r="N16" s="460"/>
+      <c r="O16" s="460"/>
+      <c r="P16" s="460" t="s">
         <v>22</v>
       </c>
-      <c r="Q15" s="92" t="s">
+      <c r="Q16" s="471" t="s">
         <v>23</v>
       </c>
-      <c r="R15" s="77"/>
-      <c r="S15" s="77"/>
-      <c r="T15" s="77"/>
-      <c r="U15" s="77"/>
-      <c r="V15" s="77"/>
-      <c r="W15" s="77"/>
-      <c r="X15" s="77"/>
-      <c r="Y15" s="77"/>
-      <c r="Z15" s="77"/>
-      <c r="AA15" s="77"/>
-      <c r="AB15" s="77"/>
-      <c r="AC15" s="77"/>
-      <c r="AD15" s="77"/>
-      <c r="AE15" s="77"/>
-      <c r="AF15" s="77"/>
-      <c r="AG15" s="77"/>
-      <c r="AH15" s="77"/>
+      <c r="R16" s="466" t="s">
+        <v>65</v>
+      </c>
+      <c r="S16" s="460"/>
+      <c r="T16" s="460"/>
+      <c r="U16" s="460"/>
+      <c r="V16" s="460"/>
+      <c r="W16" s="460"/>
+      <c r="X16" s="460"/>
+      <c r="Y16" s="460"/>
+      <c r="Z16" s="460"/>
+      <c r="AA16" s="460"/>
+      <c r="AB16" s="460"/>
+      <c r="AC16" s="460"/>
+      <c r="AD16" s="460"/>
+      <c r="AE16" s="460"/>
+      <c r="AF16" s="460"/>
+      <c r="AG16" s="460"/>
+      <c r="AH16" s="478"/>
     </row>
-    <row r="16" spans="2:36" ht="17.250000">
-      <c r="B16" s="93"/>
-      <c r="C16" s="94"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="63"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="63"/>
-      <c r="J16" s="57"/>
-      <c r="K16" s="58"/>
-      <c r="L16" s="90"/>
-      <c r="M16" s="90"/>
-      <c r="N16" s="90"/>
-      <c r="O16" s="91"/>
-      <c r="P16" s="77" t="s">
+    <row r="17" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B17" s="476"/>
+      <c r="C17" s="465"/>
+      <c r="D17" s="542"/>
+      <c r="E17" s="543"/>
+      <c r="F17" s="532"/>
+      <c r="G17" s="541"/>
+      <c r="H17" s="541"/>
+      <c r="I17" s="533"/>
+      <c r="J17" s="460" t="s">
+        <v>121</v>
+      </c>
+      <c r="K17" s="460"/>
+      <c r="L17" s="460"/>
+      <c r="M17" s="460"/>
+      <c r="N17" s="460"/>
+      <c r="O17" s="460"/>
+      <c r="P17" s="460" t="s">
         <v>22</v>
       </c>
-      <c r="Q16" s="92" t="s">
+      <c r="Q17" s="471" t="s">
         <v>23</v>
       </c>
-      <c r="R16" s="77"/>
-      <c r="S16" s="77"/>
-      <c r="T16" s="77"/>
-      <c r="U16" s="77"/>
-      <c r="V16" s="77"/>
-      <c r="W16" s="77"/>
-      <c r="X16" s="77"/>
-      <c r="Y16" s="77"/>
-      <c r="Z16" s="77"/>
-      <c r="AA16" s="77"/>
-      <c r="AB16" s="77"/>
-      <c r="AC16" s="77"/>
-      <c r="AD16" s="77"/>
-      <c r="AE16" s="77"/>
-      <c r="AF16" s="77"/>
-      <c r="AG16" s="77"/>
-      <c r="AH16" s="77"/>
+      <c r="R17" s="466" t="s">
+        <v>66</v>
+      </c>
+      <c r="S17" s="460"/>
+      <c r="T17" s="460"/>
+      <c r="U17" s="460"/>
+      <c r="V17" s="460"/>
+      <c r="W17" s="460"/>
+      <c r="X17" s="460"/>
+      <c r="Y17" s="460"/>
+      <c r="Z17" s="460"/>
+      <c r="AA17" s="460"/>
+      <c r="AB17" s="460"/>
+      <c r="AC17" s="460"/>
+      <c r="AD17" s="460"/>
+      <c r="AE17" s="460"/>
+      <c r="AF17" s="460"/>
+      <c r="AG17" s="460"/>
+      <c r="AH17" s="478"/>
     </row>
-    <row r="17" spans="2:34" ht="17.250000">
-      <c r="B17" s="93"/>
-      <c r="C17" s="94"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="63"/>
-      <c r="J17" s="57"/>
-      <c r="K17" s="58"/>
-      <c r="L17" s="90"/>
-      <c r="M17" s="90"/>
-      <c r="N17" s="90"/>
-      <c r="O17" s="91"/>
-      <c r="P17" s="77" t="s">
+    <row r="18" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B18" s="476"/>
+      <c r="C18" s="465"/>
+      <c r="D18" s="542"/>
+      <c r="E18" s="543"/>
+      <c r="F18" s="530" t="s">
+        <v>99</v>
+      </c>
+      <c r="G18" s="540"/>
+      <c r="H18" s="540"/>
+      <c r="I18" s="531"/>
+      <c r="J18" s="460" t="s">
+        <v>132</v>
+      </c>
+      <c r="K18" s="460"/>
+      <c r="L18" s="460"/>
+      <c r="M18" s="460"/>
+      <c r="N18" s="460"/>
+      <c r="O18" s="460"/>
+      <c r="P18" s="460" t="s">
         <v>22</v>
       </c>
-      <c r="Q17" s="92" t="s">
+      <c r="Q18" s="471" t="s">
         <v>23</v>
       </c>
-      <c r="R17" s="77"/>
-      <c r="S17" s="77"/>
-      <c r="T17" s="77"/>
-      <c r="U17" s="77"/>
-      <c r="V17" s="77"/>
-      <c r="W17" s="77"/>
-      <c r="X17" s="77"/>
-      <c r="Y17" s="77"/>
-      <c r="Z17" s="77"/>
-      <c r="AA17" s="77"/>
-      <c r="AB17" s="77"/>
-      <c r="AC17" s="77"/>
-      <c r="AD17" s="77"/>
-      <c r="AE17" s="77"/>
-      <c r="AF17" s="77"/>
-      <c r="AG17" s="77"/>
-      <c r="AH17" s="77"/>
+      <c r="R18" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S18" s="460"/>
+      <c r="T18" s="460"/>
+      <c r="U18" s="460"/>
+      <c r="V18" s="460"/>
+      <c r="W18" s="460"/>
+      <c r="X18" s="460"/>
+      <c r="Y18" s="460"/>
+      <c r="Z18" s="460"/>
+      <c r="AA18" s="460"/>
+      <c r="AB18" s="460"/>
+      <c r="AC18" s="460"/>
+      <c r="AD18" s="460"/>
+      <c r="AE18" s="460"/>
+      <c r="AF18" s="460"/>
+      <c r="AG18" s="460"/>
+      <c r="AH18" s="478"/>
     </row>
-    <row r="18" spans="2:34" ht="17.250000">
-      <c r="B18" s="93"/>
-      <c r="C18" s="94"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="63"/>
-      <c r="J18" s="57"/>
-      <c r="K18" s="58"/>
-      <c r="L18" s="90"/>
-      <c r="M18" s="90"/>
-      <c r="N18" s="90"/>
-      <c r="O18" s="91"/>
-      <c r="P18" s="77" t="s">
+    <row r="19" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B19" s="476"/>
+      <c r="C19" s="465"/>
+      <c r="D19" s="532"/>
+      <c r="E19" s="533"/>
+      <c r="F19" s="532"/>
+      <c r="G19" s="541"/>
+      <c r="H19" s="541"/>
+      <c r="I19" s="533"/>
+      <c r="J19" s="460" t="s">
+        <v>133</v>
+      </c>
+      <c r="K19" s="460"/>
+      <c r="L19" s="460"/>
+      <c r="M19" s="460"/>
+      <c r="N19" s="460"/>
+      <c r="O19" s="460"/>
+      <c r="P19" s="460" t="s">
         <v>22</v>
       </c>
-      <c r="Q18" s="92" t="s">
+      <c r="Q19" s="471" t="s">
         <v>23</v>
       </c>
-      <c r="R18" s="77"/>
-      <c r="S18" s="77"/>
-      <c r="T18" s="77"/>
-      <c r="U18" s="77"/>
-      <c r="V18" s="77"/>
-      <c r="W18" s="77"/>
-      <c r="X18" s="77"/>
-      <c r="Y18" s="77"/>
-      <c r="Z18" s="77"/>
-      <c r="AA18" s="77"/>
-      <c r="AB18" s="77"/>
-      <c r="AC18" s="77"/>
-      <c r="AD18" s="77"/>
-      <c r="AE18" s="77"/>
-      <c r="AF18" s="77"/>
-      <c r="AG18" s="77"/>
-      <c r="AH18" s="77"/>
+      <c r="R19" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S19" s="460"/>
+      <c r="T19" s="460"/>
+      <c r="U19" s="460"/>
+      <c r="V19" s="460"/>
+      <c r="W19" s="460"/>
+      <c r="X19" s="460"/>
+      <c r="Y19" s="460"/>
+      <c r="Z19" s="460"/>
+      <c r="AA19" s="460"/>
+      <c r="AB19" s="460"/>
+      <c r="AC19" s="460"/>
+      <c r="AD19" s="460"/>
+      <c r="AE19" s="460"/>
+      <c r="AF19" s="460"/>
+      <c r="AG19" s="460"/>
+      <c r="AH19" s="478"/>
     </row>
-    <row r="19" spans="2:34" ht="17.250000">
-      <c r="B19" s="93"/>
-      <c r="C19" s="94"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="63"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="58"/>
-      <c r="L19" s="90"/>
-      <c r="M19" s="90"/>
-      <c r="N19" s="90"/>
-      <c r="O19" s="91"/>
-      <c r="P19" s="77" t="s">
+    <row r="20" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B20" s="476"/>
+      <c r="C20" s="465"/>
+      <c r="D20" s="460" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" s="460"/>
+      <c r="F20" s="460"/>
+      <c r="G20" s="460"/>
+      <c r="H20" s="460"/>
+      <c r="I20" s="460"/>
+      <c r="J20" s="460"/>
+      <c r="K20" s="460"/>
+      <c r="L20" s="460"/>
+      <c r="M20" s="460"/>
+      <c r="N20" s="460"/>
+      <c r="O20" s="460"/>
+      <c r="P20" s="460" t="s">
         <v>22</v>
       </c>
-      <c r="Q19" s="92" t="s">
+      <c r="Q20" s="471" t="s">
         <v>23</v>
       </c>
-      <c r="R19" s="77"/>
-      <c r="S19" s="77"/>
-      <c r="T19" s="77"/>
-      <c r="U19" s="77"/>
-      <c r="V19" s="77"/>
-      <c r="W19" s="77"/>
-      <c r="X19" s="77"/>
-      <c r="Y19" s="77"/>
-      <c r="Z19" s="77"/>
-      <c r="AA19" s="77"/>
-      <c r="AB19" s="77"/>
-      <c r="AC19" s="77"/>
-      <c r="AD19" s="77"/>
-      <c r="AE19" s="77"/>
-      <c r="AF19" s="77"/>
-      <c r="AG19" s="77"/>
-      <c r="AH19" s="77"/>
+      <c r="R20" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S20" s="460"/>
+      <c r="T20" s="460"/>
+      <c r="U20" s="460"/>
+      <c r="V20" s="460"/>
+      <c r="W20" s="460"/>
+      <c r="X20" s="460"/>
+      <c r="Y20" s="460"/>
+      <c r="Z20" s="460"/>
+      <c r="AA20" s="460"/>
+      <c r="AB20" s="460"/>
+      <c r="AC20" s="460"/>
+      <c r="AD20" s="460"/>
+      <c r="AE20" s="460"/>
+      <c r="AF20" s="460"/>
+      <c r="AG20" s="460"/>
+      <c r="AH20" s="556"/>
     </row>
-    <row r="20" spans="2:34" ht="17.250000">
-      <c r="B20" s="93"/>
-      <c r="C20" s="94"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="63"/>
-      <c r="J20" s="57"/>
-      <c r="K20" s="58"/>
-      <c r="L20" s="90"/>
-      <c r="M20" s="90"/>
-      <c r="N20" s="90"/>
-      <c r="O20" s="91"/>
-      <c r="P20" s="77" t="s">
+    <row r="21" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B21" s="476"/>
+      <c r="C21" s="465"/>
+      <c r="D21" s="460" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" s="460"/>
+      <c r="F21" s="460"/>
+      <c r="G21" s="460"/>
+      <c r="H21" s="460"/>
+      <c r="I21" s="460"/>
+      <c r="J21" s="460"/>
+      <c r="K21" s="460"/>
+      <c r="L21" s="460"/>
+      <c r="M21" s="460"/>
+      <c r="N21" s="460"/>
+      <c r="O21" s="460"/>
+      <c r="P21" s="460" t="s">
         <v>22</v>
       </c>
-      <c r="Q20" s="92" t="s">
+      <c r="Q21" s="471" t="s">
         <v>23</v>
       </c>
-      <c r="R20" s="77"/>
-      <c r="S20" s="77"/>
-      <c r="T20" s="77"/>
-      <c r="U20" s="77"/>
-      <c r="V20" s="77"/>
-      <c r="W20" s="77"/>
-      <c r="X20" s="77"/>
-      <c r="Y20" s="77"/>
-      <c r="Z20" s="77"/>
-      <c r="AA20" s="77"/>
-      <c r="AB20" s="77"/>
-      <c r="AC20" s="77"/>
-      <c r="AD20" s="77"/>
-      <c r="AE20" s="77"/>
-      <c r="AF20" s="77"/>
-      <c r="AG20" s="77"/>
-      <c r="AH20" s="77"/>
+      <c r="R21" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S21" s="460"/>
+      <c r="T21" s="460"/>
+      <c r="U21" s="460"/>
+      <c r="V21" s="460"/>
+      <c r="W21" s="460"/>
+      <c r="X21" s="460"/>
+      <c r="Y21" s="460"/>
+      <c r="Z21" s="460"/>
+      <c r="AA21" s="460"/>
+      <c r="AB21" s="460"/>
+      <c r="AC21" s="460"/>
+      <c r="AD21" s="460"/>
+      <c r="AE21" s="460"/>
+      <c r="AF21" s="460"/>
+      <c r="AG21" s="460"/>
+      <c r="AH21" s="478"/>
     </row>
-    <row r="21" spans="2:34" ht="17.250000">
-      <c r="B21" s="93"/>
-      <c r="C21" s="94"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="63"/>
-      <c r="F21" s="57"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="63"/>
-      <c r="J21" s="57"/>
-      <c r="K21" s="58"/>
-      <c r="L21" s="90"/>
-      <c r="M21" s="90"/>
-      <c r="N21" s="90"/>
-      <c r="O21" s="91"/>
-      <c r="P21" s="77" t="s">
+    <row r="22" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B22" s="512"/>
+      <c r="C22" s="435"/>
+      <c r="D22" s="460"/>
+      <c r="E22" s="460"/>
+      <c r="F22" s="460"/>
+      <c r="G22" s="460"/>
+      <c r="H22" s="460"/>
+      <c r="I22" s="460"/>
+      <c r="J22" s="460"/>
+      <c r="K22" s="460"/>
+      <c r="L22" s="460"/>
+      <c r="M22" s="460"/>
+      <c r="N22" s="460"/>
+      <c r="O22" s="460"/>
+      <c r="P22" s="460" t="s">
         <v>22</v>
       </c>
-      <c r="Q21" s="92" t="s">
+      <c r="Q22" s="471" t="s">
         <v>23</v>
       </c>
-      <c r="R21" s="77"/>
-      <c r="S21" s="77"/>
-      <c r="T21" s="77"/>
-      <c r="U21" s="77"/>
-      <c r="V21" s="77"/>
-      <c r="W21" s="77"/>
-      <c r="X21" s="77"/>
-      <c r="Y21" s="77"/>
-      <c r="Z21" s="77"/>
-      <c r="AA21" s="77"/>
-      <c r="AB21" s="77"/>
-      <c r="AC21" s="77"/>
-      <c r="AD21" s="77"/>
-      <c r="AE21" s="77"/>
-      <c r="AF21" s="77"/>
-      <c r="AG21" s="77"/>
-      <c r="AH21" s="77"/>
+      <c r="R22" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S22" s="460"/>
+      <c r="T22" s="460"/>
+      <c r="U22" s="460"/>
+      <c r="V22" s="460"/>
+      <c r="W22" s="460"/>
+      <c r="X22" s="460"/>
+      <c r="Y22" s="460"/>
+      <c r="Z22" s="460"/>
+      <c r="AA22" s="460"/>
+      <c r="AB22" s="460"/>
+      <c r="AC22" s="460"/>
+      <c r="AD22" s="460"/>
+      <c r="AE22" s="460"/>
+      <c r="AF22" s="460"/>
+      <c r="AG22" s="460"/>
+      <c r="AH22" s="478"/>
     </row>
-    <row r="22" spans="2:34" ht="17.250000">
-      <c r="B22" s="93"/>
-      <c r="C22" s="94"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="63"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="63"/>
-      <c r="J22" s="57"/>
-      <c r="K22" s="58"/>
-      <c r="L22" s="90"/>
-      <c r="M22" s="90"/>
-      <c r="N22" s="90"/>
-      <c r="O22" s="91"/>
-      <c r="P22" s="77" t="s">
+    <row r="23" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B23" s="512"/>
+      <c r="C23" s="435"/>
+      <c r="D23" s="460"/>
+      <c r="E23" s="460"/>
+      <c r="F23" s="460"/>
+      <c r="G23" s="460"/>
+      <c r="H23" s="460"/>
+      <c r="I23" s="460"/>
+      <c r="J23" s="460"/>
+      <c r="K23" s="460"/>
+      <c r="L23" s="460"/>
+      <c r="M23" s="460"/>
+      <c r="N23" s="460"/>
+      <c r="O23" s="460"/>
+      <c r="P23" s="460" t="s">
         <v>22</v>
       </c>
-      <c r="Q22" s="92" t="s">
+      <c r="Q23" s="471" t="s">
         <v>23</v>
       </c>
-      <c r="R22" s="77"/>
-      <c r="S22" s="77"/>
-      <c r="T22" s="77"/>
-      <c r="U22" s="77"/>
-      <c r="V22" s="77"/>
-      <c r="W22" s="77"/>
-      <c r="X22" s="77"/>
-      <c r="Y22" s="77"/>
-      <c r="Z22" s="77"/>
-      <c r="AA22" s="77"/>
-      <c r="AB22" s="77"/>
-      <c r="AC22" s="77"/>
-      <c r="AD22" s="77"/>
-      <c r="AE22" s="77"/>
-      <c r="AF22" s="77"/>
-      <c r="AG22" s="77"/>
-      <c r="AH22" s="77"/>
+      <c r="R23" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S23" s="460"/>
+      <c r="T23" s="460"/>
+      <c r="U23" s="460"/>
+      <c r="V23" s="460"/>
+      <c r="W23" s="460"/>
+      <c r="X23" s="460"/>
+      <c r="Y23" s="460"/>
+      <c r="Z23" s="460"/>
+      <c r="AA23" s="460"/>
+      <c r="AB23" s="460"/>
+      <c r="AC23" s="460"/>
+      <c r="AD23" s="460"/>
+      <c r="AE23" s="460"/>
+      <c r="AF23" s="460"/>
+      <c r="AG23" s="460"/>
+      <c r="AH23" s="478"/>
     </row>
-    <row r="23" spans="2:34" ht="17.250000">
-      <c r="B23" s="93"/>
-      <c r="C23" s="94"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="57"/>
-      <c r="K23" s="58"/>
-      <c r="L23" s="90"/>
-      <c r="M23" s="90"/>
-      <c r="N23" s="90"/>
-      <c r="O23" s="91"/>
-      <c r="P23" s="77" t="s">
+    <row r="24" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B24" s="512"/>
+      <c r="C24" s="435"/>
+      <c r="D24" s="460"/>
+      <c r="E24" s="460"/>
+      <c r="F24" s="460"/>
+      <c r="G24" s="460"/>
+      <c r="H24" s="460"/>
+      <c r="I24" s="460"/>
+      <c r="J24" s="460"/>
+      <c r="K24" s="460"/>
+      <c r="L24" s="460"/>
+      <c r="M24" s="460"/>
+      <c r="N24" s="460"/>
+      <c r="O24" s="460"/>
+      <c r="P24" s="460" t="s">
         <v>22</v>
       </c>
-      <c r="Q23" s="92" t="s">
+      <c r="Q24" s="471" t="s">
         <v>23</v>
       </c>
-      <c r="R23" s="77"/>
-      <c r="S23" s="77"/>
-      <c r="T23" s="77"/>
-      <c r="U23" s="77"/>
-      <c r="V23" s="77"/>
-      <c r="W23" s="77"/>
-      <c r="X23" s="77"/>
-      <c r="Y23" s="77"/>
-      <c r="Z23" s="77"/>
-      <c r="AA23" s="77"/>
-      <c r="AB23" s="77"/>
-      <c r="AC23" s="77"/>
-      <c r="AD23" s="77"/>
-      <c r="AE23" s="77"/>
-      <c r="AF23" s="77"/>
-      <c r="AG23" s="77"/>
-      <c r="AH23" s="77"/>
+      <c r="R24" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S24" s="460"/>
+      <c r="T24" s="460"/>
+      <c r="U24" s="460"/>
+      <c r="V24" s="460"/>
+      <c r="W24" s="460"/>
+      <c r="X24" s="460"/>
+      <c r="Y24" s="460"/>
+      <c r="Z24" s="460"/>
+      <c r="AA24" s="460"/>
+      <c r="AB24" s="460"/>
+      <c r="AC24" s="460"/>
+      <c r="AD24" s="460"/>
+      <c r="AE24" s="460"/>
+      <c r="AF24" s="460"/>
+      <c r="AG24" s="460"/>
+      <c r="AH24" s="478"/>
     </row>
-    <row r="24" spans="2:34" ht="17.250000">
-      <c r="B24" s="93"/>
-      <c r="C24" s="94"/>
-      <c r="D24" s="57"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="57"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="63"/>
-      <c r="J24" s="57"/>
-      <c r="K24" s="58"/>
-      <c r="L24" s="90"/>
-      <c r="M24" s="90"/>
-      <c r="N24" s="90"/>
-      <c r="O24" s="91"/>
-      <c r="P24" s="77" t="s">
+    <row r="25" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B25" s="512"/>
+      <c r="C25" s="435"/>
+      <c r="D25" s="460"/>
+      <c r="E25" s="460"/>
+      <c r="F25" s="460"/>
+      <c r="G25" s="460"/>
+      <c r="H25" s="460"/>
+      <c r="I25" s="460"/>
+      <c r="J25" s="460"/>
+      <c r="K25" s="460"/>
+      <c r="L25" s="460"/>
+      <c r="M25" s="460"/>
+      <c r="N25" s="460"/>
+      <c r="O25" s="460"/>
+      <c r="P25" s="460" t="s">
         <v>22</v>
       </c>
-      <c r="Q24" s="92" t="s">
+      <c r="Q25" s="471" t="s">
         <v>23</v>
       </c>
-      <c r="R24" s="77"/>
-      <c r="S24" s="77"/>
-      <c r="T24" s="77"/>
-      <c r="U24" s="77"/>
-      <c r="V24" s="77"/>
-      <c r="W24" s="77"/>
-      <c r="X24" s="77"/>
-      <c r="Y24" s="77"/>
-      <c r="Z24" s="77"/>
-      <c r="AA24" s="77"/>
-      <c r="AB24" s="77"/>
-      <c r="AC24" s="77"/>
-      <c r="AD24" s="77"/>
-      <c r="AE24" s="77"/>
-      <c r="AF24" s="77"/>
-      <c r="AG24" s="77"/>
-      <c r="AH24" s="77"/>
+      <c r="R25" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S25" s="460"/>
+      <c r="T25" s="460"/>
+      <c r="U25" s="460"/>
+      <c r="V25" s="460"/>
+      <c r="W25" s="460"/>
+      <c r="X25" s="460"/>
+      <c r="Y25" s="460"/>
+      <c r="Z25" s="460"/>
+      <c r="AA25" s="460"/>
+      <c r="AB25" s="460"/>
+      <c r="AC25" s="460"/>
+      <c r="AD25" s="460"/>
+      <c r="AE25" s="460"/>
+      <c r="AF25" s="460"/>
+      <c r="AG25" s="460"/>
+      <c r="AH25" s="478"/>
     </row>
-    <row r="25" spans="2:34" ht="17.250000">
-      <c r="B25" s="93"/>
-      <c r="C25" s="94"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="63"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="63"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="58"/>
-      <c r="L25" s="90"/>
-      <c r="M25" s="90"/>
-      <c r="N25" s="90"/>
-      <c r="O25" s="91"/>
-      <c r="P25" s="77" t="s">
+    <row r="26" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B26" s="515" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="437"/>
+      <c r="D26" s="460" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="460"/>
+      <c r="F26" s="460" t="s">
+        <v>104</v>
+      </c>
+      <c r="G26" s="460"/>
+      <c r="H26" s="460"/>
+      <c r="I26" s="460"/>
+      <c r="J26" s="460"/>
+      <c r="K26" s="460"/>
+      <c r="L26" s="460"/>
+      <c r="M26" s="460"/>
+      <c r="N26" s="460"/>
+      <c r="O26" s="460"/>
+      <c r="P26" s="460" t="s">
         <v>22</v>
       </c>
-      <c r="Q25" s="92" t="s">
+      <c r="Q26" s="471" t="s">
         <v>23</v>
       </c>
-      <c r="R25" s="77"/>
-      <c r="S25" s="77"/>
-      <c r="T25" s="77"/>
-      <c r="U25" s="77"/>
-      <c r="V25" s="77"/>
-      <c r="W25" s="77"/>
-      <c r="X25" s="77"/>
-      <c r="Y25" s="77"/>
-      <c r="Z25" s="77"/>
-      <c r="AA25" s="77"/>
-      <c r="AB25" s="77"/>
-      <c r="AC25" s="77"/>
-      <c r="AD25" s="77"/>
-      <c r="AE25" s="77"/>
-      <c r="AF25" s="77"/>
-      <c r="AG25" s="77"/>
-      <c r="AH25" s="77"/>
+      <c r="R26" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S26" s="470"/>
+      <c r="T26" s="470"/>
+      <c r="U26" s="470"/>
+      <c r="V26" s="470"/>
+      <c r="W26" s="470"/>
+      <c r="X26" s="470"/>
+      <c r="Y26" s="470"/>
+      <c r="Z26" s="470"/>
+      <c r="AA26" s="470"/>
+      <c r="AB26" s="470"/>
+      <c r="AC26" s="470"/>
+      <c r="AD26" s="460"/>
+      <c r="AE26" s="460"/>
+      <c r="AF26" s="460"/>
+      <c r="AG26" s="470"/>
+      <c r="AH26" s="521"/>
     </row>
-    <row r="26" spans="2:34" ht="17.250000">
-      <c r="B26" s="93"/>
-      <c r="C26" s="94"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="63"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="63"/>
-      <c r="J26" s="57"/>
-      <c r="K26" s="58"/>
-      <c r="L26" s="90"/>
-      <c r="M26" s="90"/>
-      <c r="N26" s="90"/>
-      <c r="O26" s="91"/>
-      <c r="P26" s="77" t="s">
+    <row r="27" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B27" s="516"/>
+      <c r="C27" s="439"/>
+      <c r="D27" s="460" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="460"/>
+      <c r="F27" s="460" t="s">
+        <v>105</v>
+      </c>
+      <c r="G27" s="460"/>
+      <c r="H27" s="460"/>
+      <c r="I27" s="460"/>
+      <c r="J27" s="460"/>
+      <c r="K27" s="460"/>
+      <c r="L27" s="460"/>
+      <c r="M27" s="460"/>
+      <c r="N27" s="460"/>
+      <c r="O27" s="460"/>
+      <c r="P27" s="460" t="s">
         <v>22</v>
       </c>
-      <c r="Q26" s="92" t="s">
+      <c r="Q27" s="471" t="s">
         <v>23</v>
       </c>
-      <c r="R26" s="77"/>
-      <c r="S26" s="77"/>
-      <c r="T26" s="77"/>
-      <c r="U26" s="77"/>
-      <c r="V26" s="77"/>
-      <c r="W26" s="77"/>
-      <c r="X26" s="77"/>
-      <c r="Y26" s="77"/>
-      <c r="Z26" s="77"/>
-      <c r="AA26" s="77"/>
-      <c r="AB26" s="77"/>
-      <c r="AC26" s="77"/>
-      <c r="AD26" s="77"/>
-      <c r="AE26" s="77"/>
-      <c r="AF26" s="77"/>
-      <c r="AG26" s="77"/>
-      <c r="AH26" s="77"/>
+      <c r="R27" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S27" s="460"/>
+      <c r="T27" s="460"/>
+      <c r="U27" s="460"/>
+      <c r="V27" s="460"/>
+      <c r="W27" s="460"/>
+      <c r="X27" s="460"/>
+      <c r="Y27" s="460"/>
+      <c r="Z27" s="460"/>
+      <c r="AA27" s="460"/>
+      <c r="AB27" s="460"/>
+      <c r="AC27" s="460"/>
+      <c r="AD27" s="460"/>
+      <c r="AE27" s="460"/>
+      <c r="AF27" s="460"/>
+      <c r="AG27" s="460"/>
+      <c r="AH27" s="478"/>
     </row>
-    <row r="27" spans="2:34" ht="17.250000">
-      <c r="B27" s="93"/>
-      <c r="C27" s="94"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="63"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="63"/>
-      <c r="J27" s="57"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="90"/>
-      <c r="M27" s="90"/>
-      <c r="N27" s="90"/>
-      <c r="O27" s="91"/>
-      <c r="P27" s="77" t="s">
+    <row r="28" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B28" s="517"/>
+      <c r="C28" s="441"/>
+      <c r="D28" s="530" t="s">
+        <v>102</v>
+      </c>
+      <c r="E28" s="531"/>
+      <c r="F28" s="530" t="s">
+        <v>108</v>
+      </c>
+      <c r="G28" s="540"/>
+      <c r="H28" s="540"/>
+      <c r="I28" s="531"/>
+      <c r="J28" s="460" t="s">
+        <v>110</v>
+      </c>
+      <c r="K28" s="460"/>
+      <c r="L28" s="460"/>
+      <c r="M28" s="460"/>
+      <c r="N28" s="460"/>
+      <c r="O28" s="460"/>
+      <c r="P28" s="460" t="s">
         <v>22</v>
       </c>
-      <c r="Q27" s="92" t="s">
+      <c r="Q28" s="471" t="s">
         <v>23</v>
       </c>
-      <c r="R27" s="77"/>
-      <c r="S27" s="77"/>
-      <c r="T27" s="77"/>
-      <c r="U27" s="77"/>
-      <c r="V27" s="77"/>
-      <c r="W27" s="77"/>
-      <c r="X27" s="77"/>
-      <c r="Y27" s="77"/>
-      <c r="Z27" s="77"/>
-      <c r="AA27" s="77"/>
-      <c r="AB27" s="77"/>
-      <c r="AC27" s="77"/>
-      <c r="AD27" s="77"/>
-      <c r="AE27" s="77"/>
-      <c r="AF27" s="77"/>
-      <c r="AG27" s="77"/>
-      <c r="AH27" s="77"/>
+      <c r="R28" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S28" s="460"/>
+      <c r="T28" s="460"/>
+      <c r="U28" s="460"/>
+      <c r="V28" s="460"/>
+      <c r="W28" s="460"/>
+      <c r="X28" s="460"/>
+      <c r="Y28" s="460"/>
+      <c r="Z28" s="460"/>
+      <c r="AA28" s="460"/>
+      <c r="AB28" s="460"/>
+      <c r="AC28" s="460"/>
+      <c r="AD28" s="460"/>
+      <c r="AE28" s="460"/>
+      <c r="AF28" s="460"/>
+      <c r="AG28" s="460"/>
+      <c r="AH28" s="478"/>
     </row>
-    <row r="28" spans="2:34" ht="17.250000">
-      <c r="B28" s="93"/>
-      <c r="C28" s="94"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="63"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="57"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="90"/>
-      <c r="M28" s="90"/>
-      <c r="N28" s="90"/>
-      <c r="O28" s="91"/>
-      <c r="P28" s="77" t="s">
+    <row r="29" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B29" s="527"/>
+      <c r="C29" s="528"/>
+      <c r="D29" s="532"/>
+      <c r="E29" s="533"/>
+      <c r="F29" s="532"/>
+      <c r="G29" s="541"/>
+      <c r="H29" s="541"/>
+      <c r="I29" s="533"/>
+      <c r="J29" s="534" t="s">
+        <v>109</v>
+      </c>
+      <c r="K29" s="535"/>
+      <c r="L29" s="535"/>
+      <c r="M29" s="535"/>
+      <c r="N29" s="535"/>
+      <c r="O29" s="536"/>
+      <c r="P29" s="460"/>
+      <c r="Q29" s="471"/>
+      <c r="R29" s="466"/>
+      <c r="S29" s="460"/>
+      <c r="T29" s="460"/>
+      <c r="U29" s="460"/>
+      <c r="V29" s="460"/>
+      <c r="W29" s="460"/>
+      <c r="X29" s="460"/>
+      <c r="Y29" s="460"/>
+      <c r="Z29" s="460"/>
+      <c r="AA29" s="460"/>
+      <c r="AB29" s="460"/>
+      <c r="AC29" s="460"/>
+      <c r="AD29" s="460"/>
+      <c r="AE29" s="460"/>
+      <c r="AF29" s="460"/>
+      <c r="AG29" s="460"/>
+      <c r="AH29" s="478"/>
+    </row>
+    <row r="30" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B30" s="512"/>
+      <c r="C30" s="435"/>
+      <c r="D30" s="460"/>
+      <c r="E30" s="460"/>
+      <c r="F30" s="460"/>
+      <c r="G30" s="460"/>
+      <c r="H30" s="460"/>
+      <c r="I30" s="460"/>
+      <c r="J30" s="460"/>
+      <c r="K30" s="460"/>
+      <c r="L30" s="460"/>
+      <c r="M30" s="460"/>
+      <c r="N30" s="460"/>
+      <c r="O30" s="460"/>
+      <c r="P30" s="460" t="s">
         <v>22</v>
       </c>
-      <c r="Q28" s="92" t="s">
+      <c r="Q30" s="471" t="s">
         <v>23</v>
       </c>
-      <c r="R28" s="77"/>
-      <c r="S28" s="77"/>
-      <c r="T28" s="77"/>
-      <c r="U28" s="77"/>
-      <c r="V28" s="77"/>
-      <c r="W28" s="77"/>
-      <c r="X28" s="77"/>
-      <c r="Y28" s="77"/>
-      <c r="Z28" s="77"/>
-      <c r="AA28" s="77"/>
-      <c r="AB28" s="77"/>
-      <c r="AC28" s="77"/>
-      <c r="AD28" s="77"/>
-      <c r="AE28" s="77"/>
-      <c r="AF28" s="77"/>
-      <c r="AG28" s="77"/>
-      <c r="AH28" s="77"/>
+      <c r="R30" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S30" s="460"/>
+      <c r="T30" s="460"/>
+      <c r="U30" s="460"/>
+      <c r="V30" s="460"/>
+      <c r="W30" s="460"/>
+      <c r="X30" s="460"/>
+      <c r="Y30" s="460"/>
+      <c r="Z30" s="460"/>
+      <c r="AA30" s="460"/>
+      <c r="AB30" s="460"/>
+      <c r="AC30" s="460"/>
+      <c r="AD30" s="460"/>
+      <c r="AE30" s="460"/>
+      <c r="AF30" s="460"/>
+      <c r="AG30" s="460"/>
+      <c r="AH30" s="478"/>
     </row>
-    <row r="29" spans="2:34" ht="17.250000">
-      <c r="B29" s="93"/>
-      <c r="C29" s="94"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="63"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="63"/>
-      <c r="J29" s="57"/>
-      <c r="K29" s="58"/>
-      <c r="L29" s="90"/>
-      <c r="M29" s="90"/>
-      <c r="N29" s="90"/>
-      <c r="O29" s="91"/>
-      <c r="P29" s="77" t="s">
+    <row r="31" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B31" s="512"/>
+      <c r="C31" s="435"/>
+      <c r="D31" s="472"/>
+      <c r="E31" s="472"/>
+      <c r="F31" s="472"/>
+      <c r="G31" s="472"/>
+      <c r="H31" s="472"/>
+      <c r="I31" s="472"/>
+      <c r="J31" s="472"/>
+      <c r="K31" s="472"/>
+      <c r="L31" s="472"/>
+      <c r="M31" s="472"/>
+      <c r="N31" s="472"/>
+      <c r="O31" s="472"/>
+      <c r="P31" s="472" t="s">
         <v>22</v>
       </c>
-      <c r="Q29" s="92" t="s">
+      <c r="Q31" s="473" t="s">
         <v>23</v>
       </c>
-      <c r="R29" s="77"/>
-      <c r="S29" s="77"/>
-      <c r="T29" s="77"/>
-      <c r="U29" s="77"/>
-      <c r="V29" s="77"/>
-      <c r="W29" s="77"/>
-      <c r="X29" s="77"/>
-      <c r="Y29" s="77"/>
-      <c r="Z29" s="77"/>
-      <c r="AA29" s="77"/>
-      <c r="AB29" s="77"/>
-      <c r="AC29" s="77"/>
-      <c r="AD29" s="77"/>
-      <c r="AE29" s="77"/>
-      <c r="AF29" s="77"/>
-      <c r="AG29" s="77"/>
-      <c r="AH29" s="77"/>
+      <c r="R31" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S31" s="472"/>
+      <c r="T31" s="472"/>
+      <c r="U31" s="472"/>
+      <c r="V31" s="472"/>
+      <c r="W31" s="472"/>
+      <c r="X31" s="472"/>
+      <c r="Y31" s="472"/>
+      <c r="Z31" s="472"/>
+      <c r="AA31" s="472"/>
+      <c r="AB31" s="472"/>
+      <c r="AC31" s="472"/>
+      <c r="AD31" s="472"/>
+      <c r="AE31" s="472"/>
+      <c r="AF31" s="472"/>
+      <c r="AG31" s="472"/>
+      <c r="AH31" s="479"/>
     </row>
-    <row r="30" spans="2:34" ht="17.250000">
-      <c r="B30" s="93"/>
-      <c r="C30" s="94"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="63"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="58"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="63"/>
-      <c r="J30" s="57"/>
-      <c r="K30" s="58"/>
-      <c r="L30" s="90"/>
-      <c r="M30" s="90"/>
-      <c r="N30" s="90"/>
-      <c r="O30" s="91"/>
-      <c r="P30" s="77" t="s">
+    <row r="32" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B32" s="512"/>
+      <c r="C32" s="435"/>
+      <c r="D32" s="472"/>
+      <c r="E32" s="472"/>
+      <c r="F32" s="472"/>
+      <c r="G32" s="472"/>
+      <c r="H32" s="472"/>
+      <c r="I32" s="472"/>
+      <c r="J32" s="472"/>
+      <c r="K32" s="472"/>
+      <c r="L32" s="472"/>
+      <c r="M32" s="472"/>
+      <c r="N32" s="472"/>
+      <c r="O32" s="472"/>
+      <c r="P32" s="472" t="s">
         <v>22</v>
       </c>
-      <c r="Q30" s="92" t="s">
+      <c r="Q32" s="473" t="s">
         <v>23</v>
       </c>
-      <c r="R30" s="77"/>
-      <c r="S30" s="77"/>
-      <c r="T30" s="77"/>
-      <c r="U30" s="77"/>
-      <c r="V30" s="77"/>
-      <c r="W30" s="77"/>
-      <c r="X30" s="77"/>
-      <c r="Y30" s="77"/>
-      <c r="Z30" s="77"/>
-      <c r="AA30" s="77"/>
-      <c r="AB30" s="77"/>
-      <c r="AC30" s="77"/>
-      <c r="AD30" s="77"/>
-      <c r="AE30" s="77"/>
-      <c r="AF30" s="77"/>
-      <c r="AG30" s="77"/>
-      <c r="AH30" s="77"/>
+      <c r="R32" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S32" s="472"/>
+      <c r="T32" s="472"/>
+      <c r="U32" s="472"/>
+      <c r="V32" s="472"/>
+      <c r="W32" s="472"/>
+      <c r="X32" s="472"/>
+      <c r="Y32" s="472"/>
+      <c r="Z32" s="472"/>
+      <c r="AA32" s="472"/>
+      <c r="AB32" s="472"/>
+      <c r="AC32" s="472"/>
+      <c r="AD32" s="472"/>
+      <c r="AE32" s="472"/>
+      <c r="AF32" s="472"/>
+      <c r="AG32" s="472"/>
+      <c r="AH32" s="479"/>
     </row>
-    <row r="31" spans="2:34" ht="17.250000">
-      <c r="B31" s="93"/>
-      <c r="C31" s="94"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="63"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="63"/>
-      <c r="J31" s="57"/>
-      <c r="K31" s="58"/>
-      <c r="L31" s="90"/>
-      <c r="M31" s="90"/>
-      <c r="N31" s="90"/>
-      <c r="O31" s="91"/>
-      <c r="P31" s="77" t="s">
+    <row r="33" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B33" s="512"/>
+      <c r="C33" s="435"/>
+      <c r="D33" s="472"/>
+      <c r="E33" s="472"/>
+      <c r="F33" s="472"/>
+      <c r="G33" s="472"/>
+      <c r="H33" s="472"/>
+      <c r="I33" s="472"/>
+      <c r="J33" s="472"/>
+      <c r="K33" s="472"/>
+      <c r="L33" s="472"/>
+      <c r="M33" s="472"/>
+      <c r="N33" s="472"/>
+      <c r="O33" s="472"/>
+      <c r="P33" s="472" t="s">
         <v>22</v>
       </c>
-      <c r="Q31" s="92" t="s">
+      <c r="Q33" s="473" t="s">
         <v>23</v>
       </c>
-      <c r="R31" s="77"/>
-      <c r="S31" s="77"/>
-      <c r="T31" s="77"/>
-      <c r="U31" s="77"/>
-      <c r="V31" s="77"/>
-      <c r="W31" s="77"/>
-      <c r="X31" s="77"/>
-      <c r="Y31" s="77"/>
-      <c r="Z31" s="77"/>
-      <c r="AA31" s="77"/>
-      <c r="AB31" s="77"/>
-      <c r="AC31" s="77"/>
-      <c r="AD31" s="77"/>
-      <c r="AE31" s="77"/>
-      <c r="AF31" s="77"/>
-      <c r="AG31" s="77"/>
-      <c r="AH31" s="77"/>
+      <c r="R33" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S33" s="472"/>
+      <c r="T33" s="472"/>
+      <c r="U33" s="472"/>
+      <c r="V33" s="472"/>
+      <c r="W33" s="472"/>
+      <c r="X33" s="472"/>
+      <c r="Y33" s="472"/>
+      <c r="Z33" s="472"/>
+      <c r="AA33" s="472"/>
+      <c r="AB33" s="472"/>
+      <c r="AC33" s="472"/>
+      <c r="AD33" s="472"/>
+      <c r="AE33" s="472"/>
+      <c r="AF33" s="472"/>
+      <c r="AG33" s="472"/>
+      <c r="AH33" s="479"/>
     </row>
-    <row r="32" spans="2:34" ht="17.250000">
-      <c r="B32" s="93"/>
-      <c r="C32" s="94"/>
-      <c r="D32" s="57"/>
-      <c r="E32" s="63"/>
-      <c r="F32" s="57"/>
-      <c r="G32" s="58"/>
-      <c r="H32" s="58"/>
-      <c r="I32" s="63"/>
-      <c r="J32" s="57"/>
-      <c r="K32" s="58"/>
-      <c r="L32" s="90"/>
-      <c r="M32" s="90"/>
-      <c r="N32" s="90"/>
-      <c r="O32" s="91"/>
-      <c r="P32" s="77" t="s">
+    <row r="34" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B34" s="512"/>
+      <c r="C34" s="435"/>
+      <c r="D34" s="472"/>
+      <c r="E34" s="472"/>
+      <c r="F34" s="472"/>
+      <c r="G34" s="472"/>
+      <c r="H34" s="472"/>
+      <c r="I34" s="472"/>
+      <c r="J34" s="472"/>
+      <c r="K34" s="472"/>
+      <c r="L34" s="472"/>
+      <c r="M34" s="472"/>
+      <c r="N34" s="472"/>
+      <c r="O34" s="472"/>
+      <c r="P34" s="472" t="s">
         <v>22</v>
       </c>
-      <c r="Q32" s="92" t="s">
+      <c r="Q34" s="473" t="s">
         <v>23</v>
       </c>
-      <c r="R32" s="77"/>
-      <c r="S32" s="77"/>
-      <c r="T32" s="77"/>
-      <c r="U32" s="77"/>
-      <c r="V32" s="77"/>
-      <c r="W32" s="77"/>
-      <c r="X32" s="77"/>
-      <c r="Y32" s="77"/>
-      <c r="Z32" s="77"/>
-      <c r="AA32" s="77"/>
-      <c r="AB32" s="77"/>
-      <c r="AC32" s="77"/>
-      <c r="AD32" s="77"/>
-      <c r="AE32" s="77"/>
-      <c r="AF32" s="77"/>
-      <c r="AG32" s="77"/>
-      <c r="AH32" s="77"/>
+      <c r="R34" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S34" s="472"/>
+      <c r="T34" s="472"/>
+      <c r="U34" s="472"/>
+      <c r="V34" s="472"/>
+      <c r="W34" s="472"/>
+      <c r="X34" s="472"/>
+      <c r="Y34" s="472"/>
+      <c r="Z34" s="472"/>
+      <c r="AA34" s="472"/>
+      <c r="AB34" s="472"/>
+      <c r="AC34" s="472"/>
+      <c r="AD34" s="472"/>
+      <c r="AE34" s="472"/>
+      <c r="AF34" s="472"/>
+      <c r="AG34" s="472"/>
+      <c r="AH34" s="479"/>
     </row>
-    <row r="33" spans="2:34" ht="17.250000">
-      <c r="B33" s="93"/>
-      <c r="C33" s="94"/>
-      <c r="D33" s="57"/>
-      <c r="E33" s="63"/>
-      <c r="F33" s="57"/>
-      <c r="G33" s="58"/>
-      <c r="H33" s="58"/>
-      <c r="I33" s="63"/>
-      <c r="J33" s="57"/>
-      <c r="K33" s="58"/>
-      <c r="L33" s="90"/>
-      <c r="M33" s="90"/>
-      <c r="N33" s="90"/>
-      <c r="O33" s="91"/>
-      <c r="P33" s="77" t="s">
+    <row r="35" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B35" s="476" t="s">
+        <v>97</v>
+      </c>
+      <c r="C35" s="465"/>
+      <c r="D35" s="460" t="s">
+        <v>43</v>
+      </c>
+      <c r="E35" s="460"/>
+      <c r="F35" s="460" t="s">
+        <v>100</v>
+      </c>
+      <c r="G35" s="460"/>
+      <c r="H35" s="460"/>
+      <c r="I35" s="460"/>
+      <c r="J35" s="472" t="s">
+        <v>118</v>
+      </c>
+      <c r="K35" s="472"/>
+      <c r="L35" s="472"/>
+      <c r="M35" s="472"/>
+      <c r="N35" s="472"/>
+      <c r="O35" s="472"/>
+      <c r="P35" s="472" t="s">
         <v>22</v>
       </c>
-      <c r="Q33" s="92" t="s">
+      <c r="Q35" s="473" t="s">
         <v>23</v>
       </c>
-      <c r="R33" s="77"/>
-      <c r="S33" s="77"/>
-      <c r="T33" s="77"/>
-      <c r="U33" s="77"/>
-      <c r="V33" s="77"/>
-      <c r="W33" s="77"/>
-      <c r="X33" s="77"/>
-      <c r="Y33" s="77"/>
-      <c r="Z33" s="77"/>
-      <c r="AA33" s="77"/>
-      <c r="AB33" s="77"/>
-      <c r="AC33" s="77"/>
-      <c r="AD33" s="77"/>
-      <c r="AE33" s="77"/>
-      <c r="AF33" s="77"/>
-      <c r="AG33" s="77"/>
-      <c r="AH33" s="77"/>
+      <c r="R35" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S35" s="472"/>
+      <c r="T35" s="472"/>
+      <c r="U35" s="472"/>
+      <c r="V35" s="472"/>
+      <c r="W35" s="472"/>
+      <c r="X35" s="472"/>
+      <c r="Y35" s="472"/>
+      <c r="Z35" s="472"/>
+      <c r="AA35" s="472"/>
+      <c r="AB35" s="472"/>
+      <c r="AC35" s="472"/>
+      <c r="AD35" s="472"/>
+      <c r="AE35" s="472"/>
+      <c r="AF35" s="472"/>
+      <c r="AG35" s="472"/>
+      <c r="AH35" s="479"/>
     </row>
-    <row r="34" spans="2:34" ht="17.250000">
-      <c r="B34" s="93"/>
-      <c r="C34" s="94"/>
-      <c r="D34" s="57"/>
-      <c r="E34" s="63"/>
-      <c r="F34" s="57"/>
-      <c r="G34" s="58"/>
-      <c r="H34" s="58"/>
-      <c r="I34" s="63"/>
-      <c r="J34" s="57"/>
-      <c r="K34" s="58"/>
-      <c r="L34" s="90"/>
-      <c r="M34" s="90"/>
-      <c r="N34" s="90"/>
-      <c r="O34" s="91"/>
-      <c r="P34" s="77" t="s">
+    <row r="36" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B36" s="476"/>
+      <c r="C36" s="465"/>
+      <c r="D36" s="460" t="s">
+        <v>43</v>
+      </c>
+      <c r="E36" s="460"/>
+      <c r="F36" s="460" t="s">
+        <v>101</v>
+      </c>
+      <c r="G36" s="460"/>
+      <c r="H36" s="460"/>
+      <c r="I36" s="460"/>
+      <c r="J36" s="472" t="s">
+        <v>117</v>
+      </c>
+      <c r="K36" s="472"/>
+      <c r="L36" s="472"/>
+      <c r="M36" s="472"/>
+      <c r="N36" s="472"/>
+      <c r="O36" s="472"/>
+      <c r="P36" s="472" t="s">
         <v>22</v>
       </c>
-      <c r="Q34" s="92" t="s">
+      <c r="Q36" s="473" t="s">
         <v>23</v>
       </c>
-      <c r="R34" s="77"/>
-      <c r="S34" s="77"/>
-      <c r="T34" s="77"/>
-      <c r="U34" s="77"/>
-      <c r="V34" s="77"/>
-      <c r="W34" s="77"/>
-      <c r="X34" s="77"/>
-      <c r="Y34" s="77"/>
-      <c r="Z34" s="77"/>
-      <c r="AA34" s="77"/>
-      <c r="AB34" s="77"/>
-      <c r="AC34" s="77"/>
-      <c r="AD34" s="77"/>
-      <c r="AE34" s="77"/>
-      <c r="AF34" s="77"/>
-      <c r="AG34" s="77"/>
-      <c r="AH34" s="77"/>
+      <c r="R36" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S36" s="472"/>
+      <c r="T36" s="472"/>
+      <c r="U36" s="472"/>
+      <c r="V36" s="472"/>
+      <c r="W36" s="472"/>
+      <c r="X36" s="472"/>
+      <c r="Y36" s="472"/>
+      <c r="Z36" s="472"/>
+      <c r="AA36" s="472"/>
+      <c r="AB36" s="472"/>
+      <c r="AC36" s="472"/>
+      <c r="AD36" s="472"/>
+      <c r="AE36" s="472"/>
+      <c r="AF36" s="472"/>
+      <c r="AG36" s="472"/>
+      <c r="AH36" s="479"/>
     </row>
-    <row r="35" spans="2:34" ht="17.250000">
-      <c r="B35" s="93"/>
-      <c r="C35" s="94"/>
-      <c r="D35" s="57"/>
-      <c r="E35" s="63"/>
-      <c r="F35" s="57"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="63"/>
-      <c r="J35" s="57"/>
-      <c r="K35" s="58"/>
-      <c r="L35" s="90"/>
-      <c r="M35" s="90"/>
-      <c r="N35" s="90"/>
-      <c r="O35" s="91"/>
-      <c r="P35" s="77" t="s">
+    <row r="37" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B37" s="476"/>
+      <c r="C37" s="465"/>
+      <c r="D37" s="460"/>
+      <c r="E37" s="460"/>
+      <c r="F37" s="460"/>
+      <c r="G37" s="460"/>
+      <c r="H37" s="460"/>
+      <c r="I37" s="460"/>
+      <c r="J37" s="472" t="s">
+        <v>116</v>
+      </c>
+      <c r="K37" s="472"/>
+      <c r="L37" s="472"/>
+      <c r="M37" s="472"/>
+      <c r="N37" s="472"/>
+      <c r="O37" s="472"/>
+      <c r="P37" s="472" t="s">
         <v>22</v>
       </c>
-      <c r="Q35" s="92" t="s">
+      <c r="Q37" s="473" t="s">
         <v>23</v>
       </c>
-      <c r="R35" s="77"/>
-      <c r="S35" s="77"/>
-      <c r="T35" s="77"/>
-      <c r="U35" s="77"/>
-      <c r="V35" s="77"/>
-      <c r="W35" s="77"/>
-      <c r="X35" s="77"/>
-      <c r="Y35" s="77"/>
-      <c r="Z35" s="77"/>
-      <c r="AA35" s="77"/>
-      <c r="AB35" s="77"/>
-      <c r="AC35" s="77"/>
-      <c r="AD35" s="77"/>
-      <c r="AE35" s="77"/>
-      <c r="AF35" s="77"/>
-      <c r="AG35" s="77"/>
-      <c r="AH35" s="77"/>
+      <c r="R37" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S37" s="472"/>
+      <c r="T37" s="472"/>
+      <c r="U37" s="472"/>
+      <c r="V37" s="472"/>
+      <c r="W37" s="472"/>
+      <c r="X37" s="472"/>
+      <c r="Y37" s="472"/>
+      <c r="Z37" s="472"/>
+      <c r="AA37" s="472"/>
+      <c r="AB37" s="472"/>
+      <c r="AC37" s="472"/>
+      <c r="AD37" s="472"/>
+      <c r="AE37" s="472"/>
+      <c r="AF37" s="472"/>
+      <c r="AG37" s="472"/>
+      <c r="AH37" s="479"/>
     </row>
-    <row r="36" spans="2:34" ht="17.250000">
-      <c r="B36" s="93"/>
-      <c r="C36" s="94"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="63"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="58"/>
-      <c r="H36" s="58"/>
-      <c r="I36" s="63"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="58"/>
-      <c r="L36" s="90"/>
-      <c r="M36" s="90"/>
-      <c r="N36" s="90"/>
-      <c r="O36" s="91"/>
-      <c r="P36" s="77" t="s">
+    <row r="38" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B38" s="476"/>
+      <c r="C38" s="465"/>
+      <c r="D38" s="460"/>
+      <c r="E38" s="460"/>
+      <c r="F38" s="460"/>
+      <c r="G38" s="460"/>
+      <c r="H38" s="460"/>
+      <c r="I38" s="460"/>
+      <c r="J38" s="472" t="s">
+        <v>119</v>
+      </c>
+      <c r="K38" s="472"/>
+      <c r="L38" s="472"/>
+      <c r="M38" s="472"/>
+      <c r="N38" s="472"/>
+      <c r="O38" s="472"/>
+      <c r="P38" s="472" t="s">
         <v>22</v>
       </c>
-      <c r="Q36" s="92" t="s">
+      <c r="Q38" s="473" t="s">
         <v>23</v>
       </c>
-      <c r="R36" s="77"/>
-      <c r="S36" s="77"/>
-      <c r="T36" s="77"/>
-      <c r="U36" s="77"/>
-      <c r="V36" s="77"/>
-      <c r="W36" s="77"/>
-      <c r="X36" s="77"/>
-      <c r="Y36" s="77"/>
-      <c r="Z36" s="77"/>
-      <c r="AA36" s="77"/>
-      <c r="AB36" s="77"/>
-      <c r="AC36" s="77"/>
-      <c r="AD36" s="77"/>
-      <c r="AE36" s="77"/>
-      <c r="AF36" s="77"/>
-      <c r="AG36" s="77"/>
-      <c r="AH36" s="77"/>
+      <c r="R38" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S38" s="472"/>
+      <c r="T38" s="472"/>
+      <c r="U38" s="472"/>
+      <c r="V38" s="472"/>
+      <c r="W38" s="472"/>
+      <c r="X38" s="472"/>
+      <c r="Y38" s="472"/>
+      <c r="Z38" s="472"/>
+      <c r="AA38" s="472"/>
+      <c r="AB38" s="472"/>
+      <c r="AC38" s="472"/>
+      <c r="AD38" s="472"/>
+      <c r="AE38" s="472"/>
+      <c r="AF38" s="472"/>
+      <c r="AG38" s="472"/>
+      <c r="AH38" s="479"/>
     </row>
-    <row r="37" spans="2:34" ht="17.250000">
-      <c r="B37" s="95"/>
-      <c r="C37" s="97"/>
-      <c r="D37" s="57"/>
-      <c r="E37" s="63"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="58"/>
-      <c r="H37" s="58"/>
-      <c r="I37" s="63"/>
-      <c r="J37" s="57"/>
-      <c r="K37" s="58"/>
-      <c r="L37" s="90"/>
-      <c r="M37" s="90"/>
-      <c r="N37" s="90"/>
-      <c r="O37" s="91"/>
-      <c r="P37" s="77" t="s">
+    <row r="39" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B39" s="476"/>
+      <c r="C39" s="465"/>
+      <c r="D39" s="460"/>
+      <c r="E39" s="460"/>
+      <c r="F39" s="460"/>
+      <c r="G39" s="460"/>
+      <c r="H39" s="460"/>
+      <c r="I39" s="460"/>
+      <c r="J39" s="472"/>
+      <c r="K39" s="472"/>
+      <c r="L39" s="472"/>
+      <c r="M39" s="472"/>
+      <c r="N39" s="472"/>
+      <c r="O39" s="472"/>
+      <c r="P39" s="472" t="s">
         <v>22</v>
       </c>
-      <c r="Q37" s="92" t="s">
+      <c r="Q39" s="473" t="s">
         <v>23</v>
       </c>
-      <c r="R37" s="77"/>
-      <c r="S37" s="77"/>
-      <c r="T37" s="77"/>
-      <c r="U37" s="77"/>
-      <c r="V37" s="77"/>
-      <c r="W37" s="77"/>
-      <c r="X37" s="77"/>
-      <c r="Y37" s="77"/>
-      <c r="Z37" s="77"/>
-      <c r="AA37" s="77"/>
-      <c r="AB37" s="77"/>
-      <c r="AC37" s="77"/>
-      <c r="AD37" s="77"/>
-      <c r="AE37" s="77"/>
-      <c r="AF37" s="77"/>
-      <c r="AG37" s="77"/>
-      <c r="AH37" s="77"/>
+      <c r="R39" s="466" t="s">
+        <v>64</v>
+      </c>
+      <c r="S39" s="472"/>
+      <c r="T39" s="472"/>
+      <c r="U39" s="472"/>
+      <c r="V39" s="472"/>
+      <c r="W39" s="472"/>
+      <c r="X39" s="472"/>
+      <c r="Y39" s="472"/>
+      <c r="Z39" s="472"/>
+      <c r="AA39" s="472"/>
+      <c r="AB39" s="472"/>
+      <c r="AC39" s="472"/>
+      <c r="AD39" s="472"/>
+      <c r="AE39" s="472"/>
+      <c r="AF39" s="472"/>
+      <c r="AG39" s="472"/>
+      <c r="AH39" s="479"/>
+    </row>
+    <row r="40" spans="2:34" ht="17.250000" customHeight="1">
+      <c r="B40" s="476"/>
+      <c r="C40" s="465"/>
+      <c r="D40" s="472"/>
+      <c r="E40" s="472"/>
+      <c r="F40" s="472"/>
+      <c r="G40" s="472"/>
+      <c r="H40" s="472"/>
+      <c r="I40" s="472"/>
+      <c r="J40" s="483"/>
+      <c r="K40" s="483"/>
+      <c r="L40" s="483"/>
+      <c r="M40" s="483"/>
+      <c r="N40" s="483"/>
+      <c r="O40" s="483"/>
+      <c r="P40" s="483" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q40" s="484" t="s">
+        <v>23</v>
+      </c>
+      <c r="R40" s="485" t="s">
+        <v>64</v>
+      </c>
+      <c r="S40" s="483"/>
+      <c r="T40" s="483"/>
+      <c r="U40" s="483"/>
+      <c r="V40" s="483"/>
+      <c r="W40" s="483"/>
+      <c r="X40" s="483"/>
+      <c r="Y40" s="483"/>
+      <c r="Z40" s="483"/>
+      <c r="AA40" s="483"/>
+      <c r="AB40" s="483"/>
+      <c r="AC40" s="483"/>
+      <c r="AD40" s="483"/>
+      <c r="AE40" s="483"/>
+      <c r="AF40" s="483"/>
+      <c r="AG40" s="483"/>
+      <c r="AH40" s="486"/>
     </row>
   </sheetData>
-  <mergeCells count="95">
+  <mergeCells count="98">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:I2"/>
     <mergeCell ref="B3:C3"/>
@@ -3405,29 +5336,23 @@
     <mergeCell ref="T10:X10"/>
     <mergeCell ref="Y10:AC10"/>
     <mergeCell ref="AD10:AH10"/>
-    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="B12:C14"/>
+    <mergeCell ref="D12:E13"/>
     <mergeCell ref="F12:I12"/>
     <mergeCell ref="J12:O12"/>
-    <mergeCell ref="D13:E13"/>
     <mergeCell ref="F13:I13"/>
     <mergeCell ref="J13:O13"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="F14:I14"/>
     <mergeCell ref="J14:O14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="B15:C21"/>
+    <mergeCell ref="D15:E19"/>
+    <mergeCell ref="F15:I17"/>
     <mergeCell ref="J15:O15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:I16"/>
     <mergeCell ref="J16:O16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:I17"/>
     <mergeCell ref="J17:O17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="F18:I19"/>
     <mergeCell ref="J18:O18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:I19"/>
     <mergeCell ref="J19:O19"/>
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="F20:I20"/>
@@ -3447,17 +5372,16 @@
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:I25"/>
     <mergeCell ref="J25:O25"/>
+    <mergeCell ref="B26:C28"/>
     <mergeCell ref="D26:E26"/>
     <mergeCell ref="F26:I26"/>
     <mergeCell ref="J26:O26"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="F27:I27"/>
     <mergeCell ref="J27:O27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="D28:E29"/>
+    <mergeCell ref="F28:I29"/>
     <mergeCell ref="J28:O28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:I29"/>
     <mergeCell ref="J29:O29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:I30"/>
@@ -3474,6 +5398,7 @@
     <mergeCell ref="D34:E34"/>
     <mergeCell ref="F34:I34"/>
     <mergeCell ref="J34:O34"/>
+    <mergeCell ref="B35:C40"/>
     <mergeCell ref="D35:E35"/>
     <mergeCell ref="F35:I35"/>
     <mergeCell ref="J35:O35"/>
@@ -3483,6 +5408,15 @@
     <mergeCell ref="D37:E37"/>
     <mergeCell ref="F37:I37"/>
     <mergeCell ref="J37:O37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="J38:O38"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:I39"/>
+    <mergeCell ref="J39:O39"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="J40:O40"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>

--- a/타임테이블.xlsx
+++ b/타임테이블.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.292.56109"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="590" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="580" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -991,7 +991,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="61">
+  <borders count="57">
     <border>
       <left/>
       <right/>
@@ -1560,64 +1560,16 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <bottom/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
-      <left style="medium">
         <color rgb="FF000000"/>
       </left>
       <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -1794,7 +1746,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="559">
+  <cellXfs count="546">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3121,24 +3073,6 @@
     <xf numFmtId="0" fontId="48" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="35" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="36" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="37" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="55" fillId="36" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3349,70 +3283,49 @@
     <xf numFmtId="0" fontId="48" fillId="0" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="36" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="37" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="37" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="40" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="48" fillId="36" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="36" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="36" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="36" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="36" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="36" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="36" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="36" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="36" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="36" borderId="59" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="36" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="36" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3790,7 +3703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:AJ40"/>
+  <dimension ref="B2:AJ40"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
     <col min="10" max="15" width="12.00500011" customWidth="1" outlineLevel="0"/>
@@ -3898,1427 +3811,1425 @@
       <c r="I8" s="48"/>
     </row>
     <row r="9" spans="2:36" ht="18.000000">
-      <c r="B9" s="501" t="s">
+      <c r="B9" s="495" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="502"/>
-      <c r="D9" s="502" t="s">
+      <c r="C9" s="496"/>
+      <c r="D9" s="496" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="502"/>
-      <c r="F9" s="502" t="s">
+      <c r="E9" s="496"/>
+      <c r="F9" s="496" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="502"/>
-      <c r="H9" s="502"/>
-      <c r="I9" s="502"/>
-      <c r="J9" s="502" t="s">
+      <c r="G9" s="496"/>
+      <c r="H9" s="496"/>
+      <c r="I9" s="496"/>
+      <c r="J9" s="496" t="s">
         <v>9</v>
       </c>
-      <c r="K9" s="502"/>
-      <c r="L9" s="502"/>
-      <c r="M9" s="502"/>
-      <c r="N9" s="502"/>
-      <c r="O9" s="502"/>
-      <c r="P9" s="502" t="s">
+      <c r="K9" s="496"/>
+      <c r="L9" s="496"/>
+      <c r="M9" s="496"/>
+      <c r="N9" s="496"/>
+      <c r="O9" s="496"/>
+      <c r="P9" s="496" t="s">
         <v>10</v>
       </c>
-      <c r="Q9" s="502" t="s">
+      <c r="Q9" s="496" t="s">
         <v>11</v>
       </c>
-      <c r="R9" s="502" t="s">
+      <c r="R9" s="496" t="s">
         <v>13</v>
       </c>
-      <c r="S9" s="503" t="s">
+      <c r="S9" s="497" t="s">
         <v>14</v>
       </c>
-      <c r="T9" s="502" t="s">
+      <c r="T9" s="496" t="s">
         <v>21</v>
       </c>
-      <c r="U9" s="502"/>
-      <c r="V9" s="502"/>
-      <c r="W9" s="502"/>
-      <c r="X9" s="502"/>
-      <c r="Y9" s="502"/>
-      <c r="Z9" s="502"/>
-      <c r="AA9" s="502"/>
-      <c r="AB9" s="502"/>
-      <c r="AC9" s="502"/>
-      <c r="AD9" s="502"/>
-      <c r="AE9" s="502"/>
-      <c r="AF9" s="502"/>
-      <c r="AG9" s="502"/>
-      <c r="AH9" s="504"/>
+      <c r="U9" s="496"/>
+      <c r="V9" s="496"/>
+      <c r="W9" s="496"/>
+      <c r="X9" s="496"/>
+      <c r="Y9" s="496"/>
+      <c r="Z9" s="496"/>
+      <c r="AA9" s="496"/>
+      <c r="AB9" s="496"/>
+      <c r="AC9" s="496"/>
+      <c r="AD9" s="496"/>
+      <c r="AE9" s="496"/>
+      <c r="AF9" s="496"/>
+      <c r="AG9" s="496"/>
+      <c r="AH9" s="498"/>
     </row>
     <row r="10" spans="2:36" ht="18.000000">
-      <c r="B10" s="505"/>
-      <c r="C10" s="499"/>
-      <c r="D10" s="499"/>
-      <c r="E10" s="499"/>
-      <c r="F10" s="499"/>
-      <c r="G10" s="499"/>
-      <c r="H10" s="499"/>
-      <c r="I10" s="499"/>
-      <c r="J10" s="499"/>
-      <c r="K10" s="499"/>
-      <c r="L10" s="499"/>
-      <c r="M10" s="499"/>
-      <c r="N10" s="499"/>
-      <c r="O10" s="499"/>
-      <c r="P10" s="499"/>
-      <c r="Q10" s="499"/>
-      <c r="R10" s="499"/>
-      <c r="S10" s="500" t="s">
+      <c r="B10" s="499"/>
+      <c r="C10" s="493"/>
+      <c r="D10" s="493"/>
+      <c r="E10" s="493"/>
+      <c r="F10" s="493"/>
+      <c r="G10" s="493"/>
+      <c r="H10" s="493"/>
+      <c r="I10" s="493"/>
+      <c r="J10" s="493"/>
+      <c r="K10" s="493"/>
+      <c r="L10" s="493"/>
+      <c r="M10" s="493"/>
+      <c r="N10" s="493"/>
+      <c r="O10" s="493"/>
+      <c r="P10" s="493"/>
+      <c r="Q10" s="493"/>
+      <c r="R10" s="493"/>
+      <c r="S10" s="494" t="s">
         <v>15</v>
       </c>
-      <c r="T10" s="499" t="s">
+      <c r="T10" s="493" t="s">
         <v>17</v>
       </c>
-      <c r="U10" s="499"/>
-      <c r="V10" s="499"/>
-      <c r="W10" s="499"/>
-      <c r="X10" s="499"/>
-      <c r="Y10" s="499" t="s">
+      <c r="U10" s="493"/>
+      <c r="V10" s="493"/>
+      <c r="W10" s="493"/>
+      <c r="X10" s="493"/>
+      <c r="Y10" s="493" t="s">
         <v>60</v>
       </c>
-      <c r="Z10" s="499"/>
-      <c r="AA10" s="499"/>
-      <c r="AB10" s="499"/>
-      <c r="AC10" s="499"/>
-      <c r="AD10" s="499" t="s">
+      <c r="Z10" s="493"/>
+      <c r="AA10" s="493"/>
+      <c r="AB10" s="493"/>
+      <c r="AC10" s="493"/>
+      <c r="AD10" s="493" t="s">
         <v>61</v>
       </c>
-      <c r="AE10" s="499"/>
-      <c r="AF10" s="499"/>
-      <c r="AG10" s="499"/>
-      <c r="AH10" s="506"/>
+      <c r="AE10" s="493"/>
+      <c r="AF10" s="493"/>
+      <c r="AG10" s="493"/>
+      <c r="AH10" s="500"/>
       <c r="AI10" s="23"/>
       <c r="AJ10" s="23"/>
     </row>
     <row r="11" spans="2:36" ht="18.000000">
-      <c r="B11" s="507"/>
-      <c r="C11" s="500"/>
-      <c r="D11" s="499"/>
-      <c r="E11" s="499"/>
-      <c r="F11" s="499"/>
-      <c r="G11" s="499"/>
-      <c r="H11" s="499"/>
-      <c r="I11" s="499"/>
-      <c r="J11" s="499"/>
-      <c r="K11" s="499"/>
-      <c r="L11" s="499"/>
-      <c r="M11" s="499"/>
-      <c r="N11" s="499"/>
-      <c r="O11" s="499"/>
-      <c r="P11" s="500"/>
-      <c r="Q11" s="500"/>
-      <c r="R11" s="500"/>
-      <c r="S11" s="500" t="s">
+      <c r="B11" s="501"/>
+      <c r="C11" s="494"/>
+      <c r="D11" s="493"/>
+      <c r="E11" s="493"/>
+      <c r="F11" s="493"/>
+      <c r="G11" s="493"/>
+      <c r="H11" s="493"/>
+      <c r="I11" s="493"/>
+      <c r="J11" s="493"/>
+      <c r="K11" s="493"/>
+      <c r="L11" s="493"/>
+      <c r="M11" s="493"/>
+      <c r="N11" s="493"/>
+      <c r="O11" s="493"/>
+      <c r="P11" s="494"/>
+      <c r="Q11" s="494"/>
+      <c r="R11" s="494"/>
+      <c r="S11" s="494" t="s">
         <v>16</v>
       </c>
-      <c r="T11" s="500" t="s">
+      <c r="T11" s="494" t="s">
         <v>45</v>
       </c>
-      <c r="U11" s="500" t="s">
+      <c r="U11" s="494" t="s">
         <v>46</v>
       </c>
-      <c r="V11" s="500" t="s">
+      <c r="V11" s="494" t="s">
         <v>47</v>
       </c>
-      <c r="W11" s="500" t="s">
+      <c r="W11" s="494" t="s">
         <v>48</v>
       </c>
-      <c r="X11" s="500" t="s">
+      <c r="X11" s="494" t="s">
         <v>49</v>
       </c>
-      <c r="Y11" s="500" t="s">
+      <c r="Y11" s="494" t="s">
         <v>50</v>
       </c>
-      <c r="Z11" s="500" t="s">
+      <c r="Z11" s="494" t="s">
         <v>51</v>
       </c>
-      <c r="AA11" s="500" t="s">
+      <c r="AA11" s="494" t="s">
         <v>52</v>
       </c>
-      <c r="AB11" s="500" t="s">
+      <c r="AB11" s="494" t="s">
         <v>53</v>
       </c>
-      <c r="AC11" s="500" t="s">
+      <c r="AC11" s="494" t="s">
         <v>54</v>
       </c>
-      <c r="AD11" s="500" t="s">
+      <c r="AD11" s="494" t="s">
         <v>55</v>
       </c>
-      <c r="AE11" s="500" t="s">
+      <c r="AE11" s="494" t="s">
         <v>56</v>
       </c>
-      <c r="AF11" s="500" t="s">
+      <c r="AF11" s="494" t="s">
         <v>57</v>
       </c>
-      <c r="AG11" s="500" t="s">
+      <c r="AG11" s="494" t="s">
         <v>58</v>
       </c>
-      <c r="AH11" s="508" t="s">
+      <c r="AH11" s="502" t="s">
         <v>59</v>
       </c>
       <c r="AI11" s="23"/>
       <c r="AJ11" s="23"/>
     </row>
     <row r="12" spans="2:36" ht="17.250000" customHeight="1">
-      <c r="B12" s="476" t="s">
+      <c r="B12" s="470" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="465"/>
-      <c r="D12" s="545" t="s">
+      <c r="C12" s="459"/>
+      <c r="D12" s="532" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="546"/>
-      <c r="F12" s="466" t="s">
+      <c r="E12" s="533"/>
+      <c r="F12" s="460" t="s">
         <v>90</v>
       </c>
-      <c r="G12" s="466"/>
-      <c r="H12" s="466"/>
-      <c r="I12" s="466"/>
-      <c r="J12" s="466"/>
-      <c r="K12" s="466"/>
-      <c r="L12" s="466"/>
-      <c r="M12" s="466"/>
-      <c r="N12" s="466"/>
-      <c r="O12" s="466"/>
-      <c r="P12" s="466" t="s">
+      <c r="G12" s="460"/>
+      <c r="H12" s="460"/>
+      <c r="I12" s="460"/>
+      <c r="J12" s="460"/>
+      <c r="K12" s="460"/>
+      <c r="L12" s="460"/>
+      <c r="M12" s="460"/>
+      <c r="N12" s="460"/>
+      <c r="O12" s="460"/>
+      <c r="P12" s="460" t="s">
         <v>92</v>
       </c>
-      <c r="Q12" s="467">
+      <c r="Q12" s="461">
         <v>1</v>
       </c>
-      <c r="R12" s="466" t="s">
+      <c r="R12" s="460" t="s">
         <v>91</v>
       </c>
-      <c r="S12" s="468"/>
-      <c r="T12" s="468"/>
-      <c r="U12" s="468"/>
-      <c r="V12" s="466"/>
-      <c r="W12" s="466"/>
-      <c r="X12" s="466"/>
-      <c r="Y12" s="466"/>
-      <c r="Z12" s="466"/>
-      <c r="AA12" s="466"/>
-      <c r="AB12" s="466"/>
-      <c r="AC12" s="466"/>
-      <c r="AD12" s="466"/>
-      <c r="AE12" s="466"/>
-      <c r="AF12" s="466"/>
-      <c r="AG12" s="466"/>
-      <c r="AH12" s="477"/>
+      <c r="S12" s="462"/>
+      <c r="T12" s="462"/>
+      <c r="U12" s="462"/>
+      <c r="V12" s="460"/>
+      <c r="W12" s="460"/>
+      <c r="X12" s="460"/>
+      <c r="Y12" s="460"/>
+      <c r="Z12" s="460"/>
+      <c r="AA12" s="460"/>
+      <c r="AB12" s="460"/>
+      <c r="AC12" s="460"/>
+      <c r="AD12" s="460"/>
+      <c r="AE12" s="460"/>
+      <c r="AF12" s="460"/>
+      <c r="AG12" s="460"/>
+      <c r="AH12" s="471"/>
     </row>
     <row r="13" spans="2:36" ht="17.250000" customHeight="1">
-      <c r="B13" s="476"/>
-      <c r="C13" s="465"/>
-      <c r="D13" s="547"/>
-      <c r="E13" s="548"/>
-      <c r="F13" s="466" t="s">
+      <c r="B13" s="470"/>
+      <c r="C13" s="459"/>
+      <c r="D13" s="534"/>
+      <c r="E13" s="535"/>
+      <c r="F13" s="460" t="s">
         <v>128</v>
       </c>
-      <c r="G13" s="466"/>
-      <c r="H13" s="466"/>
-      <c r="I13" s="466"/>
-      <c r="J13" s="466"/>
-      <c r="K13" s="466"/>
-      <c r="L13" s="466"/>
-      <c r="M13" s="466"/>
-      <c r="N13" s="466"/>
-      <c r="O13" s="466"/>
-      <c r="P13" s="466" t="s">
+      <c r="G13" s="460"/>
+      <c r="H13" s="460"/>
+      <c r="I13" s="460"/>
+      <c r="J13" s="460"/>
+      <c r="K13" s="460"/>
+      <c r="L13" s="460"/>
+      <c r="M13" s="460"/>
+      <c r="N13" s="460"/>
+      <c r="O13" s="460"/>
+      <c r="P13" s="460" t="s">
         <v>22</v>
       </c>
-      <c r="Q13" s="469" t="s">
+      <c r="Q13" s="463" t="s">
         <v>23</v>
       </c>
-      <c r="R13" s="466" t="s">
+      <c r="R13" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S13" s="466"/>
-      <c r="T13" s="466"/>
-      <c r="U13" s="470"/>
-      <c r="V13" s="466"/>
-      <c r="W13" s="466"/>
-      <c r="X13" s="466"/>
-      <c r="Y13" s="466"/>
-      <c r="Z13" s="466"/>
-      <c r="AA13" s="466"/>
-      <c r="AB13" s="466"/>
-      <c r="AC13" s="466"/>
-      <c r="AD13" s="466"/>
-      <c r="AE13" s="466"/>
-      <c r="AF13" s="466"/>
-      <c r="AG13" s="466"/>
-      <c r="AH13" s="477"/>
+      <c r="S13" s="460"/>
+      <c r="T13" s="460"/>
+      <c r="U13" s="464"/>
+      <c r="V13" s="460"/>
+      <c r="W13" s="460"/>
+      <c r="X13" s="460"/>
+      <c r="Y13" s="460"/>
+      <c r="Z13" s="460"/>
+      <c r="AA13" s="460"/>
+      <c r="AB13" s="460"/>
+      <c r="AC13" s="460"/>
+      <c r="AD13" s="460"/>
+      <c r="AE13" s="460"/>
+      <c r="AF13" s="460"/>
+      <c r="AG13" s="460"/>
+      <c r="AH13" s="471"/>
     </row>
     <row r="14" spans="2:36" ht="17.250000" customHeight="1">
-      <c r="B14" s="476"/>
-      <c r="C14" s="465"/>
-      <c r="D14" s="460" t="s">
+      <c r="B14" s="470"/>
+      <c r="C14" s="459"/>
+      <c r="D14" s="454" t="s">
         <v>102</v>
       </c>
-      <c r="E14" s="460"/>
-      <c r="F14" s="460" t="s">
+      <c r="E14" s="454"/>
+      <c r="F14" s="454" t="s">
         <v>130</v>
       </c>
-      <c r="G14" s="460"/>
-      <c r="H14" s="460"/>
-      <c r="I14" s="460"/>
-      <c r="J14" s="460"/>
-      <c r="K14" s="460"/>
-      <c r="L14" s="460"/>
-      <c r="M14" s="460"/>
-      <c r="N14" s="460"/>
-      <c r="O14" s="460"/>
-      <c r="P14" s="460" t="s">
+      <c r="G14" s="454"/>
+      <c r="H14" s="454"/>
+      <c r="I14" s="454"/>
+      <c r="J14" s="454"/>
+      <c r="K14" s="454"/>
+      <c r="L14" s="454"/>
+      <c r="M14" s="454"/>
+      <c r="N14" s="454"/>
+      <c r="O14" s="454"/>
+      <c r="P14" s="454" t="s">
         <v>22</v>
       </c>
-      <c r="Q14" s="471" t="s">
+      <c r="Q14" s="465" t="s">
         <v>23</v>
       </c>
-      <c r="R14" s="466" t="s">
+      <c r="R14" s="460" t="s">
         <v>94</v>
       </c>
-      <c r="S14" s="460"/>
-      <c r="T14" s="460"/>
-      <c r="U14" s="470"/>
-      <c r="V14" s="460"/>
-      <c r="W14" s="460"/>
-      <c r="X14" s="460"/>
-      <c r="Y14" s="460"/>
-      <c r="Z14" s="460"/>
-      <c r="AA14" s="460"/>
-      <c r="AB14" s="460"/>
-      <c r="AC14" s="460"/>
-      <c r="AD14" s="460"/>
-      <c r="AE14" s="460"/>
-      <c r="AF14" s="460"/>
-      <c r="AG14" s="460"/>
-      <c r="AH14" s="478"/>
+      <c r="S14" s="454"/>
+      <c r="T14" s="454"/>
+      <c r="U14" s="464"/>
+      <c r="V14" s="454"/>
+      <c r="W14" s="454"/>
+      <c r="X14" s="454"/>
+      <c r="Y14" s="454"/>
+      <c r="Z14" s="454"/>
+      <c r="AA14" s="454"/>
+      <c r="AB14" s="454"/>
+      <c r="AC14" s="454"/>
+      <c r="AD14" s="454"/>
+      <c r="AE14" s="454"/>
+      <c r="AF14" s="454"/>
+      <c r="AG14" s="454"/>
+      <c r="AH14" s="472"/>
     </row>
     <row r="15" spans="2:36" ht="17.250000" customHeight="1">
-      <c r="B15" s="476" t="s">
+      <c r="B15" s="470" t="s">
         <v>95</v>
       </c>
-      <c r="C15" s="465"/>
-      <c r="D15" s="530" t="s">
+      <c r="C15" s="459"/>
+      <c r="D15" s="517" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="531"/>
-      <c r="F15" s="530" t="s">
+      <c r="E15" s="518"/>
+      <c r="F15" s="517" t="s">
         <v>98</v>
       </c>
-      <c r="G15" s="540"/>
-      <c r="H15" s="540"/>
-      <c r="I15" s="531"/>
-      <c r="J15" s="460" t="s">
+      <c r="G15" s="527"/>
+      <c r="H15" s="527"/>
+      <c r="I15" s="518"/>
+      <c r="J15" s="454" t="s">
         <v>125</v>
       </c>
-      <c r="K15" s="460"/>
-      <c r="L15" s="460"/>
-      <c r="M15" s="460"/>
-      <c r="N15" s="460"/>
-      <c r="O15" s="460"/>
-      <c r="P15" s="460" t="s">
+      <c r="K15" s="454"/>
+      <c r="L15" s="454"/>
+      <c r="M15" s="454"/>
+      <c r="N15" s="454"/>
+      <c r="O15" s="454"/>
+      <c r="P15" s="454" t="s">
         <v>22</v>
       </c>
-      <c r="Q15" s="471" t="s">
+      <c r="Q15" s="465" t="s">
         <v>23</v>
       </c>
-      <c r="R15" s="466" t="s">
+      <c r="R15" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S15" s="460"/>
-      <c r="T15" s="460"/>
-      <c r="U15" s="460"/>
-      <c r="V15" s="460"/>
-      <c r="W15" s="460"/>
-      <c r="X15" s="460"/>
-      <c r="Y15" s="460"/>
-      <c r="Z15" s="460"/>
-      <c r="AA15" s="460"/>
-      <c r="AB15" s="460"/>
-      <c r="AC15" s="460"/>
-      <c r="AD15" s="460"/>
-      <c r="AE15" s="460"/>
-      <c r="AF15" s="460"/>
-      <c r="AG15" s="460"/>
-      <c r="AH15" s="478"/>
+      <c r="S15" s="454"/>
+      <c r="T15" s="454"/>
+      <c r="U15" s="454"/>
+      <c r="V15" s="454"/>
+      <c r="W15" s="454"/>
+      <c r="X15" s="454"/>
+      <c r="Y15" s="454"/>
+      <c r="Z15" s="454"/>
+      <c r="AA15" s="454"/>
+      <c r="AB15" s="454"/>
+      <c r="AC15" s="454"/>
+      <c r="AD15" s="454"/>
+      <c r="AE15" s="454"/>
+      <c r="AF15" s="454"/>
+      <c r="AG15" s="454"/>
+      <c r="AH15" s="472"/>
     </row>
     <row r="16" spans="2:36" ht="17.250000" customHeight="1">
-      <c r="B16" s="476"/>
-      <c r="C16" s="465"/>
-      <c r="D16" s="542"/>
-      <c r="E16" s="543"/>
-      <c r="F16" s="542"/>
-      <c r="G16" s="494"/>
-      <c r="H16" s="494"/>
-      <c r="I16" s="543"/>
-      <c r="J16" s="460" t="s">
+      <c r="B16" s="470"/>
+      <c r="C16" s="459"/>
+      <c r="D16" s="529"/>
+      <c r="E16" s="530"/>
+      <c r="F16" s="529"/>
+      <c r="G16" s="488"/>
+      <c r="H16" s="488"/>
+      <c r="I16" s="530"/>
+      <c r="J16" s="454" t="s">
         <v>126</v>
       </c>
-      <c r="K16" s="460"/>
-      <c r="L16" s="460"/>
-      <c r="M16" s="460"/>
-      <c r="N16" s="460"/>
-      <c r="O16" s="460"/>
-      <c r="P16" s="460" t="s">
+      <c r="K16" s="454"/>
+      <c r="L16" s="454"/>
+      <c r="M16" s="454"/>
+      <c r="N16" s="454"/>
+      <c r="O16" s="454"/>
+      <c r="P16" s="454" t="s">
         <v>22</v>
       </c>
-      <c r="Q16" s="471" t="s">
+      <c r="Q16" s="465" t="s">
         <v>23</v>
       </c>
-      <c r="R16" s="466" t="s">
+      <c r="R16" s="460" t="s">
         <v>65</v>
       </c>
-      <c r="S16" s="460"/>
-      <c r="T16" s="460"/>
-      <c r="U16" s="460"/>
-      <c r="V16" s="460"/>
-      <c r="W16" s="460"/>
-      <c r="X16" s="460"/>
-      <c r="Y16" s="460"/>
-      <c r="Z16" s="460"/>
-      <c r="AA16" s="460"/>
-      <c r="AB16" s="460"/>
-      <c r="AC16" s="460"/>
-      <c r="AD16" s="460"/>
-      <c r="AE16" s="460"/>
-      <c r="AF16" s="460"/>
-      <c r="AG16" s="460"/>
-      <c r="AH16" s="478"/>
+      <c r="S16" s="454"/>
+      <c r="T16" s="454"/>
+      <c r="U16" s="454"/>
+      <c r="V16" s="454"/>
+      <c r="W16" s="454"/>
+      <c r="X16" s="454"/>
+      <c r="Y16" s="454"/>
+      <c r="Z16" s="454"/>
+      <c r="AA16" s="454"/>
+      <c r="AB16" s="454"/>
+      <c r="AC16" s="454"/>
+      <c r="AD16" s="454"/>
+      <c r="AE16" s="454"/>
+      <c r="AF16" s="454"/>
+      <c r="AG16" s="454"/>
+      <c r="AH16" s="472"/>
     </row>
     <row r="17" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B17" s="476"/>
-      <c r="C17" s="465"/>
-      <c r="D17" s="542"/>
-      <c r="E17" s="543"/>
-      <c r="F17" s="532"/>
-      <c r="G17" s="541"/>
-      <c r="H17" s="541"/>
-      <c r="I17" s="533"/>
-      <c r="J17" s="460" t="s">
+      <c r="B17" s="470"/>
+      <c r="C17" s="459"/>
+      <c r="D17" s="529"/>
+      <c r="E17" s="530"/>
+      <c r="F17" s="519"/>
+      <c r="G17" s="528"/>
+      <c r="H17" s="528"/>
+      <c r="I17" s="520"/>
+      <c r="J17" s="454" t="s">
         <v>121</v>
       </c>
-      <c r="K17" s="460"/>
-      <c r="L17" s="460"/>
-      <c r="M17" s="460"/>
-      <c r="N17" s="460"/>
-      <c r="O17" s="460"/>
-      <c r="P17" s="460" t="s">
+      <c r="K17" s="454"/>
+      <c r="L17" s="454"/>
+      <c r="M17" s="454"/>
+      <c r="N17" s="454"/>
+      <c r="O17" s="454"/>
+      <c r="P17" s="454" t="s">
         <v>22</v>
       </c>
-      <c r="Q17" s="471" t="s">
+      <c r="Q17" s="465" t="s">
         <v>23</v>
       </c>
-      <c r="R17" s="466" t="s">
+      <c r="R17" s="460" t="s">
         <v>66</v>
       </c>
-      <c r="S17" s="460"/>
-      <c r="T17" s="460"/>
-      <c r="U17" s="460"/>
-      <c r="V17" s="460"/>
-      <c r="W17" s="460"/>
-      <c r="X17" s="460"/>
-      <c r="Y17" s="460"/>
-      <c r="Z17" s="460"/>
-      <c r="AA17" s="460"/>
-      <c r="AB17" s="460"/>
-      <c r="AC17" s="460"/>
-      <c r="AD17" s="460"/>
-      <c r="AE17" s="460"/>
-      <c r="AF17" s="460"/>
-      <c r="AG17" s="460"/>
-      <c r="AH17" s="478"/>
+      <c r="S17" s="454"/>
+      <c r="T17" s="454"/>
+      <c r="U17" s="454"/>
+      <c r="V17" s="454"/>
+      <c r="W17" s="454"/>
+      <c r="X17" s="454"/>
+      <c r="Y17" s="454"/>
+      <c r="Z17" s="454"/>
+      <c r="AA17" s="454"/>
+      <c r="AB17" s="454"/>
+      <c r="AC17" s="454"/>
+      <c r="AD17" s="454"/>
+      <c r="AE17" s="454"/>
+      <c r="AF17" s="454"/>
+      <c r="AG17" s="454"/>
+      <c r="AH17" s="472"/>
     </row>
     <row r="18" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B18" s="476"/>
-      <c r="C18" s="465"/>
-      <c r="D18" s="542"/>
-      <c r="E18" s="543"/>
-      <c r="F18" s="530" t="s">
+      <c r="B18" s="470"/>
+      <c r="C18" s="459"/>
+      <c r="D18" s="529"/>
+      <c r="E18" s="530"/>
+      <c r="F18" s="517" t="s">
         <v>99</v>
       </c>
-      <c r="G18" s="540"/>
-      <c r="H18" s="540"/>
-      <c r="I18" s="531"/>
-      <c r="J18" s="460" t="s">
+      <c r="G18" s="527"/>
+      <c r="H18" s="527"/>
+      <c r="I18" s="518"/>
+      <c r="J18" s="454" t="s">
         <v>132</v>
       </c>
-      <c r="K18" s="460"/>
-      <c r="L18" s="460"/>
-      <c r="M18" s="460"/>
-      <c r="N18" s="460"/>
-      <c r="O18" s="460"/>
-      <c r="P18" s="460" t="s">
+      <c r="K18" s="454"/>
+      <c r="L18" s="454"/>
+      <c r="M18" s="454"/>
+      <c r="N18" s="454"/>
+      <c r="O18" s="454"/>
+      <c r="P18" s="454" t="s">
         <v>22</v>
       </c>
-      <c r="Q18" s="471" t="s">
+      <c r="Q18" s="465" t="s">
         <v>23</v>
       </c>
-      <c r="R18" s="466" t="s">
+      <c r="R18" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S18" s="460"/>
-      <c r="T18" s="460"/>
-      <c r="U18" s="460"/>
-      <c r="V18" s="460"/>
-      <c r="W18" s="460"/>
-      <c r="X18" s="460"/>
-      <c r="Y18" s="460"/>
-      <c r="Z18" s="460"/>
-      <c r="AA18" s="460"/>
-      <c r="AB18" s="460"/>
-      <c r="AC18" s="460"/>
-      <c r="AD18" s="460"/>
-      <c r="AE18" s="460"/>
-      <c r="AF18" s="460"/>
-      <c r="AG18" s="460"/>
-      <c r="AH18" s="478"/>
+      <c r="S18" s="454"/>
+      <c r="T18" s="454"/>
+      <c r="U18" s="454"/>
+      <c r="V18" s="454"/>
+      <c r="W18" s="454"/>
+      <c r="X18" s="454"/>
+      <c r="Y18" s="454"/>
+      <c r="Z18" s="454"/>
+      <c r="AA18" s="454"/>
+      <c r="AB18" s="454"/>
+      <c r="AC18" s="454"/>
+      <c r="AD18" s="454"/>
+      <c r="AE18" s="454"/>
+      <c r="AF18" s="454"/>
+      <c r="AG18" s="454"/>
+      <c r="AH18" s="472"/>
     </row>
     <row r="19" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B19" s="476"/>
-      <c r="C19" s="465"/>
-      <c r="D19" s="532"/>
-      <c r="E19" s="533"/>
-      <c r="F19" s="532"/>
-      <c r="G19" s="541"/>
-      <c r="H19" s="541"/>
-      <c r="I19" s="533"/>
-      <c r="J19" s="460" t="s">
+      <c r="B19" s="470"/>
+      <c r="C19" s="459"/>
+      <c r="D19" s="519"/>
+      <c r="E19" s="520"/>
+      <c r="F19" s="519"/>
+      <c r="G19" s="528"/>
+      <c r="H19" s="528"/>
+      <c r="I19" s="520"/>
+      <c r="J19" s="454" t="s">
         <v>133</v>
       </c>
-      <c r="K19" s="460"/>
-      <c r="L19" s="460"/>
-      <c r="M19" s="460"/>
-      <c r="N19" s="460"/>
-      <c r="O19" s="460"/>
-      <c r="P19" s="460" t="s">
+      <c r="K19" s="454"/>
+      <c r="L19" s="454"/>
+      <c r="M19" s="454"/>
+      <c r="N19" s="454"/>
+      <c r="O19" s="454"/>
+      <c r="P19" s="454" t="s">
         <v>22</v>
       </c>
-      <c r="Q19" s="471" t="s">
+      <c r="Q19" s="465" t="s">
         <v>23</v>
       </c>
-      <c r="R19" s="466" t="s">
+      <c r="R19" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S19" s="460"/>
-      <c r="T19" s="460"/>
-      <c r="U19" s="460"/>
-      <c r="V19" s="460"/>
-      <c r="W19" s="460"/>
-      <c r="X19" s="460"/>
-      <c r="Y19" s="460"/>
-      <c r="Z19" s="460"/>
-      <c r="AA19" s="460"/>
-      <c r="AB19" s="460"/>
-      <c r="AC19" s="460"/>
-      <c r="AD19" s="460"/>
-      <c r="AE19" s="460"/>
-      <c r="AF19" s="460"/>
-      <c r="AG19" s="460"/>
-      <c r="AH19" s="478"/>
+      <c r="S19" s="454"/>
+      <c r="T19" s="454"/>
+      <c r="U19" s="454"/>
+      <c r="V19" s="454"/>
+      <c r="W19" s="454"/>
+      <c r="X19" s="454"/>
+      <c r="Y19" s="454"/>
+      <c r="Z19" s="454"/>
+      <c r="AA19" s="454"/>
+      <c r="AB19" s="454"/>
+      <c r="AC19" s="454"/>
+      <c r="AD19" s="454"/>
+      <c r="AE19" s="454"/>
+      <c r="AF19" s="454"/>
+      <c r="AG19" s="454"/>
+      <c r="AH19" s="472"/>
     </row>
     <row r="20" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B20" s="476"/>
-      <c r="C20" s="465"/>
-      <c r="D20" s="460" t="s">
+      <c r="B20" s="470"/>
+      <c r="C20" s="459"/>
+      <c r="D20" s="517" t="s">
         <v>102</v>
       </c>
-      <c r="E20" s="460"/>
-      <c r="F20" s="460"/>
-      <c r="G20" s="460"/>
-      <c r="H20" s="460"/>
-      <c r="I20" s="460"/>
-      <c r="J20" s="460"/>
-      <c r="K20" s="460"/>
-      <c r="L20" s="460"/>
-      <c r="M20" s="460"/>
-      <c r="N20" s="460"/>
-      <c r="O20" s="460"/>
-      <c r="P20" s="460" t="s">
+      <c r="E20" s="518"/>
+      <c r="F20" s="454"/>
+      <c r="G20" s="454"/>
+      <c r="H20" s="454"/>
+      <c r="I20" s="454"/>
+      <c r="J20" s="454"/>
+      <c r="K20" s="454"/>
+      <c r="L20" s="454"/>
+      <c r="M20" s="454"/>
+      <c r="N20" s="454"/>
+      <c r="O20" s="454"/>
+      <c r="P20" s="454" t="s">
         <v>22</v>
       </c>
-      <c r="Q20" s="471" t="s">
+      <c r="Q20" s="465" t="s">
         <v>23</v>
       </c>
-      <c r="R20" s="466" t="s">
+      <c r="R20" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S20" s="460"/>
-      <c r="T20" s="460"/>
-      <c r="U20" s="460"/>
-      <c r="V20" s="460"/>
-      <c r="W20" s="460"/>
-      <c r="X20" s="460"/>
-      <c r="Y20" s="460"/>
-      <c r="Z20" s="460"/>
-      <c r="AA20" s="460"/>
-      <c r="AB20" s="460"/>
-      <c r="AC20" s="460"/>
-      <c r="AD20" s="460"/>
-      <c r="AE20" s="460"/>
-      <c r="AF20" s="460"/>
-      <c r="AG20" s="460"/>
-      <c r="AH20" s="556"/>
+      <c r="S20" s="454"/>
+      <c r="T20" s="454"/>
+      <c r="U20" s="454"/>
+      <c r="V20" s="454"/>
+      <c r="W20" s="454"/>
+      <c r="X20" s="454"/>
+      <c r="Y20" s="454"/>
+      <c r="Z20" s="454"/>
+      <c r="AA20" s="454"/>
+      <c r="AB20" s="454"/>
+      <c r="AC20" s="454"/>
+      <c r="AD20" s="454"/>
+      <c r="AE20" s="454"/>
+      <c r="AF20" s="454"/>
+      <c r="AG20" s="454"/>
+      <c r="AH20" s="543"/>
     </row>
     <row r="21" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B21" s="476"/>
-      <c r="C21" s="465"/>
-      <c r="D21" s="460" t="s">
-        <v>102</v>
-      </c>
-      <c r="E21" s="460"/>
-      <c r="F21" s="460"/>
-      <c r="G21" s="460"/>
-      <c r="H21" s="460"/>
-      <c r="I21" s="460"/>
-      <c r="J21" s="460"/>
-      <c r="K21" s="460"/>
-      <c r="L21" s="460"/>
-      <c r="M21" s="460"/>
-      <c r="N21" s="460"/>
-      <c r="O21" s="460"/>
-      <c r="P21" s="460" t="s">
+      <c r="B21" s="470"/>
+      <c r="C21" s="459"/>
+      <c r="D21" s="519"/>
+      <c r="E21" s="520"/>
+      <c r="F21" s="454"/>
+      <c r="G21" s="454"/>
+      <c r="H21" s="454"/>
+      <c r="I21" s="454"/>
+      <c r="J21" s="454"/>
+      <c r="K21" s="454"/>
+      <c r="L21" s="454"/>
+      <c r="M21" s="454"/>
+      <c r="N21" s="454"/>
+      <c r="O21" s="454"/>
+      <c r="P21" s="454" t="s">
         <v>22</v>
       </c>
-      <c r="Q21" s="471" t="s">
+      <c r="Q21" s="465" t="s">
         <v>23</v>
       </c>
-      <c r="R21" s="466" t="s">
+      <c r="R21" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S21" s="460"/>
-      <c r="T21" s="460"/>
-      <c r="U21" s="460"/>
-      <c r="V21" s="460"/>
-      <c r="W21" s="460"/>
-      <c r="X21" s="460"/>
-      <c r="Y21" s="460"/>
-      <c r="Z21" s="460"/>
-      <c r="AA21" s="460"/>
-      <c r="AB21" s="460"/>
-      <c r="AC21" s="460"/>
-      <c r="AD21" s="460"/>
-      <c r="AE21" s="460"/>
-      <c r="AF21" s="460"/>
-      <c r="AG21" s="460"/>
-      <c r="AH21" s="478"/>
+      <c r="S21" s="454"/>
+      <c r="T21" s="454"/>
+      <c r="U21" s="454"/>
+      <c r="V21" s="454"/>
+      <c r="W21" s="454"/>
+      <c r="X21" s="454"/>
+      <c r="Y21" s="454"/>
+      <c r="Z21" s="454"/>
+      <c r="AA21" s="454"/>
+      <c r="AB21" s="454"/>
+      <c r="AC21" s="454"/>
+      <c r="AD21" s="454"/>
+      <c r="AE21" s="454"/>
+      <c r="AF21" s="454"/>
+      <c r="AG21" s="454"/>
+      <c r="AH21" s="472"/>
     </row>
     <row r="22" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B22" s="512"/>
+      <c r="B22" s="506"/>
       <c r="C22" s="435"/>
-      <c r="D22" s="460"/>
-      <c r="E22" s="460"/>
-      <c r="F22" s="460"/>
-      <c r="G22" s="460"/>
-      <c r="H22" s="460"/>
-      <c r="I22" s="460"/>
-      <c r="J22" s="460"/>
-      <c r="K22" s="460"/>
-      <c r="L22" s="460"/>
-      <c r="M22" s="460"/>
-      <c r="N22" s="460"/>
-      <c r="O22" s="460"/>
-      <c r="P22" s="460" t="s">
+      <c r="D22" s="454"/>
+      <c r="E22" s="454"/>
+      <c r="F22" s="454"/>
+      <c r="G22" s="454"/>
+      <c r="H22" s="454"/>
+      <c r="I22" s="454"/>
+      <c r="J22" s="454"/>
+      <c r="K22" s="454"/>
+      <c r="L22" s="454"/>
+      <c r="M22" s="454"/>
+      <c r="N22" s="454"/>
+      <c r="O22" s="454"/>
+      <c r="P22" s="454" t="s">
         <v>22</v>
       </c>
-      <c r="Q22" s="471" t="s">
+      <c r="Q22" s="465" t="s">
         <v>23</v>
       </c>
-      <c r="R22" s="466" t="s">
+      <c r="R22" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S22" s="460"/>
-      <c r="T22" s="460"/>
-      <c r="U22" s="460"/>
-      <c r="V22" s="460"/>
-      <c r="W22" s="460"/>
-      <c r="X22" s="460"/>
-      <c r="Y22" s="460"/>
-      <c r="Z22" s="460"/>
-      <c r="AA22" s="460"/>
-      <c r="AB22" s="460"/>
-      <c r="AC22" s="460"/>
-      <c r="AD22" s="460"/>
-      <c r="AE22" s="460"/>
-      <c r="AF22" s="460"/>
-      <c r="AG22" s="460"/>
-      <c r="AH22" s="478"/>
+      <c r="S22" s="454"/>
+      <c r="T22" s="454"/>
+      <c r="U22" s="454"/>
+      <c r="V22" s="454"/>
+      <c r="W22" s="454"/>
+      <c r="X22" s="454"/>
+      <c r="Y22" s="454"/>
+      <c r="Z22" s="454"/>
+      <c r="AA22" s="454"/>
+      <c r="AB22" s="454"/>
+      <c r="AC22" s="454"/>
+      <c r="AD22" s="454"/>
+      <c r="AE22" s="454"/>
+      <c r="AF22" s="454"/>
+      <c r="AG22" s="454"/>
+      <c r="AH22" s="472"/>
     </row>
     <row r="23" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B23" s="512"/>
+      <c r="B23" s="506"/>
       <c r="C23" s="435"/>
-      <c r="D23" s="460"/>
-      <c r="E23" s="460"/>
-      <c r="F23" s="460"/>
-      <c r="G23" s="460"/>
-      <c r="H23" s="460"/>
-      <c r="I23" s="460"/>
-      <c r="J23" s="460"/>
-      <c r="K23" s="460"/>
-      <c r="L23" s="460"/>
-      <c r="M23" s="460"/>
-      <c r="N23" s="460"/>
-      <c r="O23" s="460"/>
-      <c r="P23" s="460" t="s">
+      <c r="D23" s="454"/>
+      <c r="E23" s="454"/>
+      <c r="F23" s="454"/>
+      <c r="G23" s="454"/>
+      <c r="H23" s="454"/>
+      <c r="I23" s="454"/>
+      <c r="J23" s="454"/>
+      <c r="K23" s="454"/>
+      <c r="L23" s="454"/>
+      <c r="M23" s="454"/>
+      <c r="N23" s="454"/>
+      <c r="O23" s="454"/>
+      <c r="P23" s="454" t="s">
         <v>22</v>
       </c>
-      <c r="Q23" s="471" t="s">
+      <c r="Q23" s="465" t="s">
         <v>23</v>
       </c>
-      <c r="R23" s="466" t="s">
+      <c r="R23" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S23" s="460"/>
-      <c r="T23" s="460"/>
-      <c r="U23" s="460"/>
-      <c r="V23" s="460"/>
-      <c r="W23" s="460"/>
-      <c r="X23" s="460"/>
-      <c r="Y23" s="460"/>
-      <c r="Z23" s="460"/>
-      <c r="AA23" s="460"/>
-      <c r="AB23" s="460"/>
-      <c r="AC23" s="460"/>
-      <c r="AD23" s="460"/>
-      <c r="AE23" s="460"/>
-      <c r="AF23" s="460"/>
-      <c r="AG23" s="460"/>
-      <c r="AH23" s="478"/>
+      <c r="S23" s="454"/>
+      <c r="T23" s="454"/>
+      <c r="U23" s="454"/>
+      <c r="V23" s="454"/>
+      <c r="W23" s="454"/>
+      <c r="X23" s="454"/>
+      <c r="Y23" s="454"/>
+      <c r="Z23" s="454"/>
+      <c r="AA23" s="454"/>
+      <c r="AB23" s="454"/>
+      <c r="AC23" s="454"/>
+      <c r="AD23" s="454"/>
+      <c r="AE23" s="454"/>
+      <c r="AF23" s="454"/>
+      <c r="AG23" s="454"/>
+      <c r="AH23" s="472"/>
     </row>
     <row r="24" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B24" s="512"/>
+      <c r="B24" s="506"/>
       <c r="C24" s="435"/>
-      <c r="D24" s="460"/>
-      <c r="E24" s="460"/>
-      <c r="F24" s="460"/>
-      <c r="G24" s="460"/>
-      <c r="H24" s="460"/>
-      <c r="I24" s="460"/>
-      <c r="J24" s="460"/>
-      <c r="K24" s="460"/>
-      <c r="L24" s="460"/>
-      <c r="M24" s="460"/>
-      <c r="N24" s="460"/>
-      <c r="O24" s="460"/>
-      <c r="P24" s="460" t="s">
+      <c r="D24" s="454"/>
+      <c r="E24" s="454"/>
+      <c r="F24" s="454"/>
+      <c r="G24" s="454"/>
+      <c r="H24" s="454"/>
+      <c r="I24" s="454"/>
+      <c r="J24" s="454"/>
+      <c r="K24" s="454"/>
+      <c r="L24" s="454"/>
+      <c r="M24" s="454"/>
+      <c r="N24" s="454"/>
+      <c r="O24" s="454"/>
+      <c r="P24" s="454" t="s">
         <v>22</v>
       </c>
-      <c r="Q24" s="471" t="s">
+      <c r="Q24" s="465" t="s">
         <v>23</v>
       </c>
-      <c r="R24" s="466" t="s">
+      <c r="R24" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S24" s="460"/>
-      <c r="T24" s="460"/>
-      <c r="U24" s="460"/>
-      <c r="V24" s="460"/>
-      <c r="W24" s="460"/>
-      <c r="X24" s="460"/>
-      <c r="Y24" s="460"/>
-      <c r="Z24" s="460"/>
-      <c r="AA24" s="460"/>
-      <c r="AB24" s="460"/>
-      <c r="AC24" s="460"/>
-      <c r="AD24" s="460"/>
-      <c r="AE24" s="460"/>
-      <c r="AF24" s="460"/>
-      <c r="AG24" s="460"/>
-      <c r="AH24" s="478"/>
+      <c r="S24" s="454"/>
+      <c r="T24" s="454"/>
+      <c r="U24" s="454"/>
+      <c r="V24" s="454"/>
+      <c r="W24" s="454"/>
+      <c r="X24" s="454"/>
+      <c r="Y24" s="454"/>
+      <c r="Z24" s="454"/>
+      <c r="AA24" s="454"/>
+      <c r="AB24" s="454"/>
+      <c r="AC24" s="454"/>
+      <c r="AD24" s="454"/>
+      <c r="AE24" s="454"/>
+      <c r="AF24" s="454"/>
+      <c r="AG24" s="454"/>
+      <c r="AH24" s="472"/>
     </row>
     <row r="25" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B25" s="512"/>
+      <c r="B25" s="506"/>
       <c r="C25" s="435"/>
-      <c r="D25" s="460"/>
-      <c r="E25" s="460"/>
-      <c r="F25" s="460"/>
-      <c r="G25" s="460"/>
-      <c r="H25" s="460"/>
-      <c r="I25" s="460"/>
-      <c r="J25" s="460"/>
-      <c r="K25" s="460"/>
-      <c r="L25" s="460"/>
-      <c r="M25" s="460"/>
-      <c r="N25" s="460"/>
-      <c r="O25" s="460"/>
-      <c r="P25" s="460" t="s">
+      <c r="D25" s="454"/>
+      <c r="E25" s="454"/>
+      <c r="F25" s="454"/>
+      <c r="G25" s="454"/>
+      <c r="H25" s="454"/>
+      <c r="I25" s="454"/>
+      <c r="J25" s="454"/>
+      <c r="K25" s="454"/>
+      <c r="L25" s="454"/>
+      <c r="M25" s="454"/>
+      <c r="N25" s="454"/>
+      <c r="O25" s="454"/>
+      <c r="P25" s="454" t="s">
         <v>22</v>
       </c>
-      <c r="Q25" s="471" t="s">
+      <c r="Q25" s="465" t="s">
         <v>23</v>
       </c>
-      <c r="R25" s="466" t="s">
+      <c r="R25" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S25" s="460"/>
-      <c r="T25" s="460"/>
-      <c r="U25" s="460"/>
-      <c r="V25" s="460"/>
-      <c r="W25" s="460"/>
-      <c r="X25" s="460"/>
-      <c r="Y25" s="460"/>
-      <c r="Z25" s="460"/>
-      <c r="AA25" s="460"/>
-      <c r="AB25" s="460"/>
-      <c r="AC25" s="460"/>
-      <c r="AD25" s="460"/>
-      <c r="AE25" s="460"/>
-      <c r="AF25" s="460"/>
-      <c r="AG25" s="460"/>
-      <c r="AH25" s="478"/>
+      <c r="S25" s="454"/>
+      <c r="T25" s="454"/>
+      <c r="U25" s="454"/>
+      <c r="V25" s="454"/>
+      <c r="W25" s="454"/>
+      <c r="X25" s="454"/>
+      <c r="Y25" s="454"/>
+      <c r="Z25" s="454"/>
+      <c r="AA25" s="454"/>
+      <c r="AB25" s="454"/>
+      <c r="AC25" s="454"/>
+      <c r="AD25" s="454"/>
+      <c r="AE25" s="454"/>
+      <c r="AF25" s="454"/>
+      <c r="AG25" s="454"/>
+      <c r="AH25" s="472"/>
     </row>
     <row r="26" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B26" s="515" t="s">
+      <c r="B26" s="509" t="s">
         <v>96</v>
       </c>
       <c r="C26" s="437"/>
-      <c r="D26" s="460" t="s">
+      <c r="D26" s="454" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="460"/>
-      <c r="F26" s="460" t="s">
+      <c r="E26" s="454"/>
+      <c r="F26" s="454" t="s">
         <v>104</v>
       </c>
-      <c r="G26" s="460"/>
-      <c r="H26" s="460"/>
-      <c r="I26" s="460"/>
-      <c r="J26" s="460"/>
-      <c r="K26" s="460"/>
-      <c r="L26" s="460"/>
-      <c r="M26" s="460"/>
-      <c r="N26" s="460"/>
-      <c r="O26" s="460"/>
-      <c r="P26" s="460" t="s">
+      <c r="G26" s="454"/>
+      <c r="H26" s="454"/>
+      <c r="I26" s="454"/>
+      <c r="J26" s="454"/>
+      <c r="K26" s="454"/>
+      <c r="L26" s="454"/>
+      <c r="M26" s="454"/>
+      <c r="N26" s="454"/>
+      <c r="O26" s="454"/>
+      <c r="P26" s="454" t="s">
         <v>22</v>
       </c>
-      <c r="Q26" s="471" t="s">
+      <c r="Q26" s="465" t="s">
         <v>23</v>
       </c>
-      <c r="R26" s="466" t="s">
+      <c r="R26" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S26" s="470"/>
-      <c r="T26" s="470"/>
-      <c r="U26" s="470"/>
-      <c r="V26" s="470"/>
-      <c r="W26" s="470"/>
-      <c r="X26" s="470"/>
-      <c r="Y26" s="470"/>
-      <c r="Z26" s="470"/>
-      <c r="AA26" s="470"/>
-      <c r="AB26" s="470"/>
-      <c r="AC26" s="470"/>
-      <c r="AD26" s="460"/>
-      <c r="AE26" s="460"/>
-      <c r="AF26" s="460"/>
-      <c r="AG26" s="470"/>
-      <c r="AH26" s="521"/>
+      <c r="S26" s="464"/>
+      <c r="T26" s="464"/>
+      <c r="U26" s="464"/>
+      <c r="V26" s="464"/>
+      <c r="W26" s="464"/>
+      <c r="X26" s="464"/>
+      <c r="Y26" s="464"/>
+      <c r="Z26" s="464"/>
+      <c r="AA26" s="464"/>
+      <c r="AB26" s="464"/>
+      <c r="AC26" s="464"/>
+      <c r="AD26" s="454"/>
+      <c r="AE26" s="454"/>
+      <c r="AF26" s="454"/>
+      <c r="AG26" s="464"/>
+      <c r="AH26" s="513"/>
     </row>
     <row r="27" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B27" s="516"/>
+      <c r="B27" s="510"/>
       <c r="C27" s="439"/>
-      <c r="D27" s="460" t="s">
+      <c r="D27" s="454" t="s">
         <v>43</v>
       </c>
-      <c r="E27" s="460"/>
-      <c r="F27" s="460" t="s">
+      <c r="E27" s="454"/>
+      <c r="F27" s="454" t="s">
         <v>105</v>
       </c>
-      <c r="G27" s="460"/>
-      <c r="H27" s="460"/>
-      <c r="I27" s="460"/>
-      <c r="J27" s="460"/>
-      <c r="K27" s="460"/>
-      <c r="L27" s="460"/>
-      <c r="M27" s="460"/>
-      <c r="N27" s="460"/>
-      <c r="O27" s="460"/>
-      <c r="P27" s="460" t="s">
+      <c r="G27" s="454"/>
+      <c r="H27" s="454"/>
+      <c r="I27" s="454"/>
+      <c r="J27" s="454"/>
+      <c r="K27" s="454"/>
+      <c r="L27" s="454"/>
+      <c r="M27" s="454"/>
+      <c r="N27" s="454"/>
+      <c r="O27" s="454"/>
+      <c r="P27" s="454" t="s">
         <v>22</v>
       </c>
-      <c r="Q27" s="471" t="s">
+      <c r="Q27" s="465" t="s">
         <v>23</v>
       </c>
-      <c r="R27" s="466" t="s">
+      <c r="R27" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S27" s="460"/>
-      <c r="T27" s="460"/>
-      <c r="U27" s="460"/>
-      <c r="V27" s="460"/>
-      <c r="W27" s="460"/>
-      <c r="X27" s="460"/>
-      <c r="Y27" s="460"/>
-      <c r="Z27" s="460"/>
-      <c r="AA27" s="460"/>
-      <c r="AB27" s="460"/>
-      <c r="AC27" s="460"/>
-      <c r="AD27" s="460"/>
-      <c r="AE27" s="460"/>
-      <c r="AF27" s="460"/>
-      <c r="AG27" s="460"/>
-      <c r="AH27" s="478"/>
+      <c r="S27" s="454"/>
+      <c r="T27" s="454"/>
+      <c r="U27" s="454"/>
+      <c r="V27" s="454"/>
+      <c r="W27" s="454"/>
+      <c r="X27" s="454"/>
+      <c r="Y27" s="454"/>
+      <c r="Z27" s="454"/>
+      <c r="AA27" s="454"/>
+      <c r="AB27" s="454"/>
+      <c r="AC27" s="454"/>
+      <c r="AD27" s="454"/>
+      <c r="AE27" s="454"/>
+      <c r="AF27" s="454"/>
+      <c r="AG27" s="454"/>
+      <c r="AH27" s="472"/>
     </row>
     <row r="28" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B28" s="517"/>
+      <c r="B28" s="511"/>
       <c r="C28" s="441"/>
-      <c r="D28" s="530" t="s">
+      <c r="D28" s="517" t="s">
         <v>102</v>
       </c>
-      <c r="E28" s="531"/>
-      <c r="F28" s="530" t="s">
+      <c r="E28" s="518"/>
+      <c r="F28" s="517" t="s">
         <v>108</v>
       </c>
-      <c r="G28" s="540"/>
-      <c r="H28" s="540"/>
-      <c r="I28" s="531"/>
-      <c r="J28" s="460" t="s">
+      <c r="G28" s="527"/>
+      <c r="H28" s="527"/>
+      <c r="I28" s="518"/>
+      <c r="J28" s="454" t="s">
         <v>110</v>
       </c>
-      <c r="K28" s="460"/>
-      <c r="L28" s="460"/>
-      <c r="M28" s="460"/>
-      <c r="N28" s="460"/>
-      <c r="O28" s="460"/>
-      <c r="P28" s="460" t="s">
+      <c r="K28" s="454"/>
+      <c r="L28" s="454"/>
+      <c r="M28" s="454"/>
+      <c r="N28" s="454"/>
+      <c r="O28" s="454"/>
+      <c r="P28" s="454" t="s">
         <v>22</v>
       </c>
-      <c r="Q28" s="471" t="s">
+      <c r="Q28" s="465" t="s">
         <v>23</v>
       </c>
-      <c r="R28" s="466" t="s">
+      <c r="R28" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S28" s="460"/>
-      <c r="T28" s="460"/>
-      <c r="U28" s="460"/>
-      <c r="V28" s="460"/>
-      <c r="W28" s="460"/>
-      <c r="X28" s="460"/>
-      <c r="Y28" s="460"/>
-      <c r="Z28" s="460"/>
-      <c r="AA28" s="460"/>
-      <c r="AB28" s="460"/>
-      <c r="AC28" s="460"/>
-      <c r="AD28" s="460"/>
-      <c r="AE28" s="460"/>
-      <c r="AF28" s="460"/>
-      <c r="AG28" s="460"/>
-      <c r="AH28" s="478"/>
+      <c r="S28" s="454"/>
+      <c r="T28" s="454"/>
+      <c r="U28" s="454"/>
+      <c r="V28" s="454"/>
+      <c r="W28" s="454"/>
+      <c r="X28" s="454"/>
+      <c r="Y28" s="454"/>
+      <c r="Z28" s="454"/>
+      <c r="AA28" s="454"/>
+      <c r="AB28" s="454"/>
+      <c r="AC28" s="454"/>
+      <c r="AD28" s="454"/>
+      <c r="AE28" s="454"/>
+      <c r="AF28" s="454"/>
+      <c r="AG28" s="454"/>
+      <c r="AH28" s="472"/>
     </row>
     <row r="29" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B29" s="527"/>
-      <c r="C29" s="528"/>
-      <c r="D29" s="532"/>
-      <c r="E29" s="533"/>
-      <c r="F29" s="532"/>
-      <c r="G29" s="541"/>
-      <c r="H29" s="541"/>
-      <c r="I29" s="533"/>
-      <c r="J29" s="534" t="s">
+      <c r="B29" s="511"/>
+      <c r="C29" s="441"/>
+      <c r="D29" s="519"/>
+      <c r="E29" s="520"/>
+      <c r="F29" s="519"/>
+      <c r="G29" s="528"/>
+      <c r="H29" s="528"/>
+      <c r="I29" s="520"/>
+      <c r="J29" s="521" t="s">
         <v>109</v>
       </c>
-      <c r="K29" s="535"/>
-      <c r="L29" s="535"/>
-      <c r="M29" s="535"/>
-      <c r="N29" s="535"/>
-      <c r="O29" s="536"/>
-      <c r="P29" s="460"/>
-      <c r="Q29" s="471"/>
-      <c r="R29" s="466"/>
-      <c r="S29" s="460"/>
-      <c r="T29" s="460"/>
-      <c r="U29" s="460"/>
-      <c r="V29" s="460"/>
-      <c r="W29" s="460"/>
-      <c r="X29" s="460"/>
-      <c r="Y29" s="460"/>
-      <c r="Z29" s="460"/>
-      <c r="AA29" s="460"/>
-      <c r="AB29" s="460"/>
-      <c r="AC29" s="460"/>
-      <c r="AD29" s="460"/>
-      <c r="AE29" s="460"/>
-      <c r="AF29" s="460"/>
-      <c r="AG29" s="460"/>
-      <c r="AH29" s="478"/>
+      <c r="K29" s="522"/>
+      <c r="L29" s="522"/>
+      <c r="M29" s="522"/>
+      <c r="N29" s="522"/>
+      <c r="O29" s="523"/>
+      <c r="P29" s="454"/>
+      <c r="Q29" s="465"/>
+      <c r="R29" s="460"/>
+      <c r="S29" s="454"/>
+      <c r="T29" s="454"/>
+      <c r="U29" s="454"/>
+      <c r="V29" s="454"/>
+      <c r="W29" s="454"/>
+      <c r="X29" s="454"/>
+      <c r="Y29" s="454"/>
+      <c r="Z29" s="454"/>
+      <c r="AA29" s="454"/>
+      <c r="AB29" s="454"/>
+      <c r="AC29" s="454"/>
+      <c r="AD29" s="454"/>
+      <c r="AE29" s="454"/>
+      <c r="AF29" s="454"/>
+      <c r="AG29" s="454"/>
+      <c r="AH29" s="472"/>
     </row>
     <row r="30" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B30" s="512"/>
+      <c r="B30" s="506"/>
       <c r="C30" s="435"/>
-      <c r="D30" s="460"/>
-      <c r="E30" s="460"/>
-      <c r="F30" s="460"/>
-      <c r="G30" s="460"/>
-      <c r="H30" s="460"/>
-      <c r="I30" s="460"/>
-      <c r="J30" s="460"/>
-      <c r="K30" s="460"/>
-      <c r="L30" s="460"/>
-      <c r="M30" s="460"/>
-      <c r="N30" s="460"/>
-      <c r="O30" s="460"/>
-      <c r="P30" s="460" t="s">
+      <c r="D30" s="454"/>
+      <c r="E30" s="454"/>
+      <c r="F30" s="454"/>
+      <c r="G30" s="454"/>
+      <c r="H30" s="454"/>
+      <c r="I30" s="454"/>
+      <c r="J30" s="454"/>
+      <c r="K30" s="454"/>
+      <c r="L30" s="454"/>
+      <c r="M30" s="454"/>
+      <c r="N30" s="454"/>
+      <c r="O30" s="454"/>
+      <c r="P30" s="454" t="s">
         <v>22</v>
       </c>
-      <c r="Q30" s="471" t="s">
+      <c r="Q30" s="465" t="s">
         <v>23</v>
       </c>
-      <c r="R30" s="466" t="s">
+      <c r="R30" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S30" s="460"/>
-      <c r="T30" s="460"/>
-      <c r="U30" s="460"/>
-      <c r="V30" s="460"/>
-      <c r="W30" s="460"/>
-      <c r="X30" s="460"/>
-      <c r="Y30" s="460"/>
-      <c r="Z30" s="460"/>
-      <c r="AA30" s="460"/>
-      <c r="AB30" s="460"/>
-      <c r="AC30" s="460"/>
-      <c r="AD30" s="460"/>
-      <c r="AE30" s="460"/>
-      <c r="AF30" s="460"/>
-      <c r="AG30" s="460"/>
-      <c r="AH30" s="478"/>
+      <c r="S30" s="454"/>
+      <c r="T30" s="454"/>
+      <c r="U30" s="454"/>
+      <c r="V30" s="454"/>
+      <c r="W30" s="454"/>
+      <c r="X30" s="454"/>
+      <c r="Y30" s="454"/>
+      <c r="Z30" s="454"/>
+      <c r="AA30" s="454"/>
+      <c r="AB30" s="454"/>
+      <c r="AC30" s="454"/>
+      <c r="AD30" s="454"/>
+      <c r="AE30" s="454"/>
+      <c r="AF30" s="454"/>
+      <c r="AG30" s="454"/>
+      <c r="AH30" s="472"/>
     </row>
     <row r="31" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B31" s="512"/>
+      <c r="B31" s="506"/>
       <c r="C31" s="435"/>
-      <c r="D31" s="472"/>
-      <c r="E31" s="472"/>
-      <c r="F31" s="472"/>
-      <c r="G31" s="472"/>
-      <c r="H31" s="472"/>
-      <c r="I31" s="472"/>
-      <c r="J31" s="472"/>
-      <c r="K31" s="472"/>
-      <c r="L31" s="472"/>
-      <c r="M31" s="472"/>
-      <c r="N31" s="472"/>
-      <c r="O31" s="472"/>
-      <c r="P31" s="472" t="s">
+      <c r="D31" s="466"/>
+      <c r="E31" s="466"/>
+      <c r="F31" s="466"/>
+      <c r="G31" s="466"/>
+      <c r="H31" s="466"/>
+      <c r="I31" s="466"/>
+      <c r="J31" s="466"/>
+      <c r="K31" s="466"/>
+      <c r="L31" s="466"/>
+      <c r="M31" s="466"/>
+      <c r="N31" s="466"/>
+      <c r="O31" s="466"/>
+      <c r="P31" s="466" t="s">
         <v>22</v>
       </c>
-      <c r="Q31" s="473" t="s">
+      <c r="Q31" s="467" t="s">
         <v>23</v>
       </c>
-      <c r="R31" s="466" t="s">
+      <c r="R31" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S31" s="472"/>
-      <c r="T31" s="472"/>
-      <c r="U31" s="472"/>
-      <c r="V31" s="472"/>
-      <c r="W31" s="472"/>
-      <c r="X31" s="472"/>
-      <c r="Y31" s="472"/>
-      <c r="Z31" s="472"/>
-      <c r="AA31" s="472"/>
-      <c r="AB31" s="472"/>
-      <c r="AC31" s="472"/>
-      <c r="AD31" s="472"/>
-      <c r="AE31" s="472"/>
-      <c r="AF31" s="472"/>
-      <c r="AG31" s="472"/>
-      <c r="AH31" s="479"/>
+      <c r="S31" s="466"/>
+      <c r="T31" s="466"/>
+      <c r="U31" s="466"/>
+      <c r="V31" s="466"/>
+      <c r="W31" s="466"/>
+      <c r="X31" s="466"/>
+      <c r="Y31" s="466"/>
+      <c r="Z31" s="466"/>
+      <c r="AA31" s="466"/>
+      <c r="AB31" s="466"/>
+      <c r="AC31" s="466"/>
+      <c r="AD31" s="466"/>
+      <c r="AE31" s="466"/>
+      <c r="AF31" s="466"/>
+      <c r="AG31" s="466"/>
+      <c r="AH31" s="473"/>
     </row>
     <row r="32" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B32" s="512"/>
+      <c r="B32" s="506"/>
       <c r="C32" s="435"/>
-      <c r="D32" s="472"/>
-      <c r="E32" s="472"/>
-      <c r="F32" s="472"/>
-      <c r="G32" s="472"/>
-      <c r="H32" s="472"/>
-      <c r="I32" s="472"/>
-      <c r="J32" s="472"/>
-      <c r="K32" s="472"/>
-      <c r="L32" s="472"/>
-      <c r="M32" s="472"/>
-      <c r="N32" s="472"/>
-      <c r="O32" s="472"/>
-      <c r="P32" s="472" t="s">
+      <c r="D32" s="466"/>
+      <c r="E32" s="466"/>
+      <c r="F32" s="466"/>
+      <c r="G32" s="466"/>
+      <c r="H32" s="466"/>
+      <c r="I32" s="466"/>
+      <c r="J32" s="466"/>
+      <c r="K32" s="466"/>
+      <c r="L32" s="466"/>
+      <c r="M32" s="466"/>
+      <c r="N32" s="466"/>
+      <c r="O32" s="466"/>
+      <c r="P32" s="466" t="s">
         <v>22</v>
       </c>
-      <c r="Q32" s="473" t="s">
+      <c r="Q32" s="467" t="s">
         <v>23</v>
       </c>
-      <c r="R32" s="466" t="s">
+      <c r="R32" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S32" s="472"/>
-      <c r="T32" s="472"/>
-      <c r="U32" s="472"/>
-      <c r="V32" s="472"/>
-      <c r="W32" s="472"/>
-      <c r="X32" s="472"/>
-      <c r="Y32" s="472"/>
-      <c r="Z32" s="472"/>
-      <c r="AA32" s="472"/>
-      <c r="AB32" s="472"/>
-      <c r="AC32" s="472"/>
-      <c r="AD32" s="472"/>
-      <c r="AE32" s="472"/>
-      <c r="AF32" s="472"/>
-      <c r="AG32" s="472"/>
-      <c r="AH32" s="479"/>
+      <c r="S32" s="466"/>
+      <c r="T32" s="466"/>
+      <c r="U32" s="466"/>
+      <c r="V32" s="466"/>
+      <c r="W32" s="466"/>
+      <c r="X32" s="466"/>
+      <c r="Y32" s="466"/>
+      <c r="Z32" s="466"/>
+      <c r="AA32" s="466"/>
+      <c r="AB32" s="466"/>
+      <c r="AC32" s="466"/>
+      <c r="AD32" s="466"/>
+      <c r="AE32" s="466"/>
+      <c r="AF32" s="466"/>
+      <c r="AG32" s="466"/>
+      <c r="AH32" s="473"/>
     </row>
     <row r="33" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B33" s="512"/>
+      <c r="B33" s="506"/>
       <c r="C33" s="435"/>
-      <c r="D33" s="472"/>
-      <c r="E33" s="472"/>
-      <c r="F33" s="472"/>
-      <c r="G33" s="472"/>
-      <c r="H33" s="472"/>
-      <c r="I33" s="472"/>
-      <c r="J33" s="472"/>
-      <c r="K33" s="472"/>
-      <c r="L33" s="472"/>
-      <c r="M33" s="472"/>
-      <c r="N33" s="472"/>
-      <c r="O33" s="472"/>
-      <c r="P33" s="472" t="s">
+      <c r="D33" s="466"/>
+      <c r="E33" s="466"/>
+      <c r="F33" s="466"/>
+      <c r="G33" s="466"/>
+      <c r="H33" s="466"/>
+      <c r="I33" s="466"/>
+      <c r="J33" s="466"/>
+      <c r="K33" s="466"/>
+      <c r="L33" s="466"/>
+      <c r="M33" s="466"/>
+      <c r="N33" s="466"/>
+      <c r="O33" s="466"/>
+      <c r="P33" s="466" t="s">
         <v>22</v>
       </c>
-      <c r="Q33" s="473" t="s">
+      <c r="Q33" s="467" t="s">
         <v>23</v>
       </c>
-      <c r="R33" s="466" t="s">
+      <c r="R33" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S33" s="472"/>
-      <c r="T33" s="472"/>
-      <c r="U33" s="472"/>
-      <c r="V33" s="472"/>
-      <c r="W33" s="472"/>
-      <c r="X33" s="472"/>
-      <c r="Y33" s="472"/>
-      <c r="Z33" s="472"/>
-      <c r="AA33" s="472"/>
-      <c r="AB33" s="472"/>
-      <c r="AC33" s="472"/>
-      <c r="AD33" s="472"/>
-      <c r="AE33" s="472"/>
-      <c r="AF33" s="472"/>
-      <c r="AG33" s="472"/>
-      <c r="AH33" s="479"/>
+      <c r="S33" s="466"/>
+      <c r="T33" s="466"/>
+      <c r="U33" s="466"/>
+      <c r="V33" s="466"/>
+      <c r="W33" s="466"/>
+      <c r="X33" s="466"/>
+      <c r="Y33" s="466"/>
+      <c r="Z33" s="466"/>
+      <c r="AA33" s="466"/>
+      <c r="AB33" s="466"/>
+      <c r="AC33" s="466"/>
+      <c r="AD33" s="466"/>
+      <c r="AE33" s="466"/>
+      <c r="AF33" s="466"/>
+      <c r="AG33" s="466"/>
+      <c r="AH33" s="473"/>
     </row>
     <row r="34" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B34" s="512"/>
+      <c r="B34" s="506"/>
       <c r="C34" s="435"/>
-      <c r="D34" s="472"/>
-      <c r="E34" s="472"/>
-      <c r="F34" s="472"/>
-      <c r="G34" s="472"/>
-      <c r="H34" s="472"/>
-      <c r="I34" s="472"/>
-      <c r="J34" s="472"/>
-      <c r="K34" s="472"/>
-      <c r="L34" s="472"/>
-      <c r="M34" s="472"/>
-      <c r="N34" s="472"/>
-      <c r="O34" s="472"/>
-      <c r="P34" s="472" t="s">
+      <c r="D34" s="466"/>
+      <c r="E34" s="466"/>
+      <c r="F34" s="466"/>
+      <c r="G34" s="466"/>
+      <c r="H34" s="466"/>
+      <c r="I34" s="466"/>
+      <c r="J34" s="466"/>
+      <c r="K34" s="466"/>
+      <c r="L34" s="466"/>
+      <c r="M34" s="466"/>
+      <c r="N34" s="466"/>
+      <c r="O34" s="466"/>
+      <c r="P34" s="466" t="s">
         <v>22</v>
       </c>
-      <c r="Q34" s="473" t="s">
+      <c r="Q34" s="467" t="s">
         <v>23</v>
       </c>
-      <c r="R34" s="466" t="s">
+      <c r="R34" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S34" s="472"/>
-      <c r="T34" s="472"/>
-      <c r="U34" s="472"/>
-      <c r="V34" s="472"/>
-      <c r="W34" s="472"/>
-      <c r="X34" s="472"/>
-      <c r="Y34" s="472"/>
-      <c r="Z34" s="472"/>
-      <c r="AA34" s="472"/>
-      <c r="AB34" s="472"/>
-      <c r="AC34" s="472"/>
-      <c r="AD34" s="472"/>
-      <c r="AE34" s="472"/>
-      <c r="AF34" s="472"/>
-      <c r="AG34" s="472"/>
-      <c r="AH34" s="479"/>
+      <c r="S34" s="466"/>
+      <c r="T34" s="466"/>
+      <c r="U34" s="466"/>
+      <c r="V34" s="466"/>
+      <c r="W34" s="466"/>
+      <c r="X34" s="466"/>
+      <c r="Y34" s="466"/>
+      <c r="Z34" s="466"/>
+      <c r="AA34" s="466"/>
+      <c r="AB34" s="466"/>
+      <c r="AC34" s="466"/>
+      <c r="AD34" s="466"/>
+      <c r="AE34" s="466"/>
+      <c r="AF34" s="466"/>
+      <c r="AG34" s="466"/>
+      <c r="AH34" s="473"/>
     </row>
     <row r="35" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B35" s="476" t="s">
+      <c r="B35" s="470" t="s">
         <v>97</v>
       </c>
-      <c r="C35" s="465"/>
-      <c r="D35" s="460" t="s">
+      <c r="C35" s="459"/>
+      <c r="D35" s="454" t="s">
         <v>43</v>
       </c>
-      <c r="E35" s="460"/>
-      <c r="F35" s="460" t="s">
+      <c r="E35" s="454"/>
+      <c r="F35" s="454" t="s">
         <v>100</v>
       </c>
-      <c r="G35" s="460"/>
-      <c r="H35" s="460"/>
-      <c r="I35" s="460"/>
-      <c r="J35" s="472" t="s">
+      <c r="G35" s="454"/>
+      <c r="H35" s="454"/>
+      <c r="I35" s="454"/>
+      <c r="J35" s="466" t="s">
         <v>118</v>
       </c>
-      <c r="K35" s="472"/>
-      <c r="L35" s="472"/>
-      <c r="M35" s="472"/>
-      <c r="N35" s="472"/>
-      <c r="O35" s="472"/>
-      <c r="P35" s="472" t="s">
+      <c r="K35" s="466"/>
+      <c r="L35" s="466"/>
+      <c r="M35" s="466"/>
+      <c r="N35" s="466"/>
+      <c r="O35" s="466"/>
+      <c r="P35" s="466" t="s">
         <v>22</v>
       </c>
-      <c r="Q35" s="473" t="s">
+      <c r="Q35" s="467" t="s">
         <v>23</v>
       </c>
-      <c r="R35" s="466" t="s">
+      <c r="R35" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S35" s="472"/>
-      <c r="T35" s="472"/>
-      <c r="U35" s="472"/>
-      <c r="V35" s="472"/>
-      <c r="W35" s="472"/>
-      <c r="X35" s="472"/>
-      <c r="Y35" s="472"/>
-      <c r="Z35" s="472"/>
-      <c r="AA35" s="472"/>
-      <c r="AB35" s="472"/>
-      <c r="AC35" s="472"/>
-      <c r="AD35" s="472"/>
-      <c r="AE35" s="472"/>
-      <c r="AF35" s="472"/>
-      <c r="AG35" s="472"/>
-      <c r="AH35" s="479"/>
+      <c r="S35" s="466"/>
+      <c r="T35" s="466"/>
+      <c r="U35" s="466"/>
+      <c r="V35" s="466"/>
+      <c r="W35" s="466"/>
+      <c r="X35" s="466"/>
+      <c r="Y35" s="466"/>
+      <c r="Z35" s="466"/>
+      <c r="AA35" s="466"/>
+      <c r="AB35" s="466"/>
+      <c r="AC35" s="466"/>
+      <c r="AD35" s="466"/>
+      <c r="AE35" s="466"/>
+      <c r="AF35" s="466"/>
+      <c r="AG35" s="466"/>
+      <c r="AH35" s="473"/>
     </row>
     <row r="36" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B36" s="476"/>
-      <c r="C36" s="465"/>
-      <c r="D36" s="460" t="s">
+      <c r="B36" s="470"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="454" t="s">
         <v>43</v>
       </c>
-      <c r="E36" s="460"/>
-      <c r="F36" s="460" t="s">
+      <c r="E36" s="454"/>
+      <c r="F36" s="454" t="s">
         <v>101</v>
       </c>
-      <c r="G36" s="460"/>
-      <c r="H36" s="460"/>
-      <c r="I36" s="460"/>
-      <c r="J36" s="472" t="s">
+      <c r="G36" s="454"/>
+      <c r="H36" s="454"/>
+      <c r="I36" s="454"/>
+      <c r="J36" s="466" t="s">
         <v>117</v>
       </c>
-      <c r="K36" s="472"/>
-      <c r="L36" s="472"/>
-      <c r="M36" s="472"/>
-      <c r="N36" s="472"/>
-      <c r="O36" s="472"/>
-      <c r="P36" s="472" t="s">
+      <c r="K36" s="466"/>
+      <c r="L36" s="466"/>
+      <c r="M36" s="466"/>
+      <c r="N36" s="466"/>
+      <c r="O36" s="466"/>
+      <c r="P36" s="466" t="s">
         <v>22</v>
       </c>
-      <c r="Q36" s="473" t="s">
+      <c r="Q36" s="467" t="s">
         <v>23</v>
       </c>
-      <c r="R36" s="466" t="s">
+      <c r="R36" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S36" s="472"/>
-      <c r="T36" s="472"/>
-      <c r="U36" s="472"/>
-      <c r="V36" s="472"/>
-      <c r="W36" s="472"/>
-      <c r="X36" s="472"/>
-      <c r="Y36" s="472"/>
-      <c r="Z36" s="472"/>
-      <c r="AA36" s="472"/>
-      <c r="AB36" s="472"/>
-      <c r="AC36" s="472"/>
-      <c r="AD36" s="472"/>
-      <c r="AE36" s="472"/>
-      <c r="AF36" s="472"/>
-      <c r="AG36" s="472"/>
-      <c r="AH36" s="479"/>
+      <c r="S36" s="466"/>
+      <c r="T36" s="466"/>
+      <c r="U36" s="466"/>
+      <c r="V36" s="466"/>
+      <c r="W36" s="466"/>
+      <c r="X36" s="466"/>
+      <c r="Y36" s="466"/>
+      <c r="Z36" s="466"/>
+      <c r="AA36" s="466"/>
+      <c r="AB36" s="466"/>
+      <c r="AC36" s="466"/>
+      <c r="AD36" s="466"/>
+      <c r="AE36" s="466"/>
+      <c r="AF36" s="466"/>
+      <c r="AG36" s="466"/>
+      <c r="AH36" s="473"/>
     </row>
     <row r="37" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B37" s="476"/>
-      <c r="C37" s="465"/>
-      <c r="D37" s="460"/>
-      <c r="E37" s="460"/>
-      <c r="F37" s="460"/>
-      <c r="G37" s="460"/>
-      <c r="H37" s="460"/>
-      <c r="I37" s="460"/>
-      <c r="J37" s="472" t="s">
+      <c r="B37" s="470"/>
+      <c r="C37" s="459"/>
+      <c r="D37" s="454"/>
+      <c r="E37" s="454"/>
+      <c r="F37" s="454"/>
+      <c r="G37" s="454"/>
+      <c r="H37" s="454"/>
+      <c r="I37" s="454"/>
+      <c r="J37" s="466" t="s">
         <v>116</v>
       </c>
-      <c r="K37" s="472"/>
-      <c r="L37" s="472"/>
-      <c r="M37" s="472"/>
-      <c r="N37" s="472"/>
-      <c r="O37" s="472"/>
-      <c r="P37" s="472" t="s">
+      <c r="K37" s="466"/>
+      <c r="L37" s="466"/>
+      <c r="M37" s="466"/>
+      <c r="N37" s="466"/>
+      <c r="O37" s="466"/>
+      <c r="P37" s="466" t="s">
         <v>22</v>
       </c>
-      <c r="Q37" s="473" t="s">
+      <c r="Q37" s="467" t="s">
         <v>23</v>
       </c>
-      <c r="R37" s="466" t="s">
+      <c r="R37" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S37" s="472"/>
-      <c r="T37" s="472"/>
-      <c r="U37" s="472"/>
-      <c r="V37" s="472"/>
-      <c r="W37" s="472"/>
-      <c r="X37" s="472"/>
-      <c r="Y37" s="472"/>
-      <c r="Z37" s="472"/>
-      <c r="AA37" s="472"/>
-      <c r="AB37" s="472"/>
-      <c r="AC37" s="472"/>
-      <c r="AD37" s="472"/>
-      <c r="AE37" s="472"/>
-      <c r="AF37" s="472"/>
-      <c r="AG37" s="472"/>
-      <c r="AH37" s="479"/>
+      <c r="S37" s="466"/>
+      <c r="T37" s="466"/>
+      <c r="U37" s="466"/>
+      <c r="V37" s="466"/>
+      <c r="W37" s="466"/>
+      <c r="X37" s="466"/>
+      <c r="Y37" s="466"/>
+      <c r="Z37" s="466"/>
+      <c r="AA37" s="466"/>
+      <c r="AB37" s="466"/>
+      <c r="AC37" s="466"/>
+      <c r="AD37" s="466"/>
+      <c r="AE37" s="466"/>
+      <c r="AF37" s="466"/>
+      <c r="AG37" s="466"/>
+      <c r="AH37" s="473"/>
     </row>
     <row r="38" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B38" s="476"/>
-      <c r="C38" s="465"/>
-      <c r="D38" s="460"/>
-      <c r="E38" s="460"/>
-      <c r="F38" s="460"/>
-      <c r="G38" s="460"/>
-      <c r="H38" s="460"/>
-      <c r="I38" s="460"/>
-      <c r="J38" s="472" t="s">
+      <c r="B38" s="470"/>
+      <c r="C38" s="459"/>
+      <c r="D38" s="454"/>
+      <c r="E38" s="454"/>
+      <c r="F38" s="454"/>
+      <c r="G38" s="454"/>
+      <c r="H38" s="454"/>
+      <c r="I38" s="454"/>
+      <c r="J38" s="466" t="s">
         <v>119</v>
       </c>
-      <c r="K38" s="472"/>
-      <c r="L38" s="472"/>
-      <c r="M38" s="472"/>
-      <c r="N38" s="472"/>
-      <c r="O38" s="472"/>
-      <c r="P38" s="472" t="s">
+      <c r="K38" s="466"/>
+      <c r="L38" s="466"/>
+      <c r="M38" s="466"/>
+      <c r="N38" s="466"/>
+      <c r="O38" s="466"/>
+      <c r="P38" s="466" t="s">
         <v>22</v>
       </c>
-      <c r="Q38" s="473" t="s">
+      <c r="Q38" s="467" t="s">
         <v>23</v>
       </c>
-      <c r="R38" s="466" t="s">
+      <c r="R38" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S38" s="472"/>
-      <c r="T38" s="472"/>
-      <c r="U38" s="472"/>
-      <c r="V38" s="472"/>
-      <c r="W38" s="472"/>
-      <c r="X38" s="472"/>
-      <c r="Y38" s="472"/>
-      <c r="Z38" s="472"/>
-      <c r="AA38" s="472"/>
-      <c r="AB38" s="472"/>
-      <c r="AC38" s="472"/>
-      <c r="AD38" s="472"/>
-      <c r="AE38" s="472"/>
-      <c r="AF38" s="472"/>
-      <c r="AG38" s="472"/>
-      <c r="AH38" s="479"/>
+      <c r="S38" s="466"/>
+      <c r="T38" s="466"/>
+      <c r="U38" s="466"/>
+      <c r="V38" s="466"/>
+      <c r="W38" s="466"/>
+      <c r="X38" s="466"/>
+      <c r="Y38" s="466"/>
+      <c r="Z38" s="466"/>
+      <c r="AA38" s="466"/>
+      <c r="AB38" s="466"/>
+      <c r="AC38" s="466"/>
+      <c r="AD38" s="466"/>
+      <c r="AE38" s="466"/>
+      <c r="AF38" s="466"/>
+      <c r="AG38" s="466"/>
+      <c r="AH38" s="473"/>
     </row>
     <row r="39" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B39" s="476"/>
-      <c r="C39" s="465"/>
-      <c r="D39" s="460"/>
-      <c r="E39" s="460"/>
-      <c r="F39" s="460"/>
-      <c r="G39" s="460"/>
-      <c r="H39" s="460"/>
-      <c r="I39" s="460"/>
-      <c r="J39" s="472"/>
-      <c r="K39" s="472"/>
-      <c r="L39" s="472"/>
-      <c r="M39" s="472"/>
-      <c r="N39" s="472"/>
-      <c r="O39" s="472"/>
-      <c r="P39" s="472" t="s">
+      <c r="B39" s="470"/>
+      <c r="C39" s="459"/>
+      <c r="D39" s="454"/>
+      <c r="E39" s="454"/>
+      <c r="F39" s="454"/>
+      <c r="G39" s="454"/>
+      <c r="H39" s="454"/>
+      <c r="I39" s="454"/>
+      <c r="J39" s="466"/>
+      <c r="K39" s="466"/>
+      <c r="L39" s="466"/>
+      <c r="M39" s="466"/>
+      <c r="N39" s="466"/>
+      <c r="O39" s="466"/>
+      <c r="P39" s="466" t="s">
         <v>22</v>
       </c>
-      <c r="Q39" s="473" t="s">
+      <c r="Q39" s="467" t="s">
         <v>23</v>
       </c>
-      <c r="R39" s="466" t="s">
+      <c r="R39" s="460" t="s">
         <v>64</v>
       </c>
-      <c r="S39" s="472"/>
-      <c r="T39" s="472"/>
-      <c r="U39" s="472"/>
-      <c r="V39" s="472"/>
-      <c r="W39" s="472"/>
-      <c r="X39" s="472"/>
-      <c r="Y39" s="472"/>
-      <c r="Z39" s="472"/>
-      <c r="AA39" s="472"/>
-      <c r="AB39" s="472"/>
-      <c r="AC39" s="472"/>
-      <c r="AD39" s="472"/>
-      <c r="AE39" s="472"/>
-      <c r="AF39" s="472"/>
-      <c r="AG39" s="472"/>
-      <c r="AH39" s="479"/>
+      <c r="S39" s="466"/>
+      <c r="T39" s="466"/>
+      <c r="U39" s="466"/>
+      <c r="V39" s="466"/>
+      <c r="W39" s="466"/>
+      <c r="X39" s="466"/>
+      <c r="Y39" s="466"/>
+      <c r="Z39" s="466"/>
+      <c r="AA39" s="466"/>
+      <c r="AB39" s="466"/>
+      <c r="AC39" s="466"/>
+      <c r="AD39" s="466"/>
+      <c r="AE39" s="466"/>
+      <c r="AF39" s="466"/>
+      <c r="AG39" s="466"/>
+      <c r="AH39" s="473"/>
     </row>
     <row r="40" spans="2:34" ht="17.250000" customHeight="1">
-      <c r="B40" s="476"/>
-      <c r="C40" s="465"/>
-      <c r="D40" s="472"/>
-      <c r="E40" s="472"/>
-      <c r="F40" s="472"/>
-      <c r="G40" s="472"/>
-      <c r="H40" s="472"/>
-      <c r="I40" s="472"/>
-      <c r="J40" s="483"/>
-      <c r="K40" s="483"/>
-      <c r="L40" s="483"/>
-      <c r="M40" s="483"/>
-      <c r="N40" s="483"/>
-      <c r="O40" s="483"/>
-      <c r="P40" s="483" t="s">
+      <c r="B40" s="470"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="466"/>
+      <c r="E40" s="466"/>
+      <c r="F40" s="466"/>
+      <c r="G40" s="466"/>
+      <c r="H40" s="466"/>
+      <c r="I40" s="466"/>
+      <c r="J40" s="477"/>
+      <c r="K40" s="477"/>
+      <c r="L40" s="477"/>
+      <c r="M40" s="477"/>
+      <c r="N40" s="477"/>
+      <c r="O40" s="477"/>
+      <c r="P40" s="477" t="s">
         <v>22</v>
       </c>
-      <c r="Q40" s="484" t="s">
+      <c r="Q40" s="478" t="s">
         <v>23</v>
       </c>
-      <c r="R40" s="485" t="s">
+      <c r="R40" s="479" t="s">
         <v>64</v>
       </c>
-      <c r="S40" s="483"/>
-      <c r="T40" s="483"/>
-      <c r="U40" s="483"/>
-      <c r="V40" s="483"/>
-      <c r="W40" s="483"/>
-      <c r="X40" s="483"/>
-      <c r="Y40" s="483"/>
-      <c r="Z40" s="483"/>
-      <c r="AA40" s="483"/>
-      <c r="AB40" s="483"/>
-      <c r="AC40" s="483"/>
-      <c r="AD40" s="483"/>
-      <c r="AE40" s="483"/>
-      <c r="AF40" s="483"/>
-      <c r="AG40" s="483"/>
-      <c r="AH40" s="486"/>
+      <c r="S40" s="477"/>
+      <c r="T40" s="477"/>
+      <c r="U40" s="477"/>
+      <c r="V40" s="477"/>
+      <c r="W40" s="477"/>
+      <c r="X40" s="477"/>
+      <c r="Y40" s="477"/>
+      <c r="Z40" s="477"/>
+      <c r="AA40" s="477"/>
+      <c r="AB40" s="477"/>
+      <c r="AC40" s="477"/>
+      <c r="AD40" s="477"/>
+      <c r="AE40" s="477"/>
+      <c r="AF40" s="477"/>
+      <c r="AG40" s="477"/>
+      <c r="AH40" s="480"/>
     </row>
   </sheetData>
-  <mergeCells count="98">
+  <mergeCells count="97">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:I2"/>
     <mergeCell ref="B3:C3"/>
@@ -5354,10 +5265,9 @@
     <mergeCell ref="F18:I19"/>
     <mergeCell ref="J18:O18"/>
     <mergeCell ref="J19:O19"/>
-    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D20:E21"/>
     <mergeCell ref="F20:I20"/>
     <mergeCell ref="J20:O20"/>
-    <mergeCell ref="D21:E21"/>
     <mergeCell ref="F21:I21"/>
     <mergeCell ref="J21:O21"/>
     <mergeCell ref="D22:E22"/>
